--- a/data/sxbet/ligas/UEFA Conference League/trades.xlsx
+++ b/data/sxbet/ligas/UEFA Conference League/trades.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,39 +531,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x7de08a0243073e49c6e479dead7f166232ecd3480830513fb8953abf4d30f575</t>
+          <t>0xb86a834aa70af447f0675d386c1849b1c99fbb8415a4a0f57dedbfc3374369c8</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>10.74</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.2875</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Vardar</t>
-        </is>
-      </c>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -571,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Riga FC vs Vardar</t>
+          <t>KF Drita vs Floriana</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Riga FC</t>
+          <t>KF Drita</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Floriana</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x3df545e9e324274c452d3611c5ff53dc80c8487fce47da81056d17c1b4257d63</t>
+          <t>0x74cee3640eed67802d8602418d415d7e5f881528425b4aded0a73b883c57f7c2</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19548393</t>
+          <t>L19556829</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785064838</t>
+          <t>1785068425</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785258000</t>
+          <t>1785261600</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>13.333333</t>
+          <t>37.356522</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,7 +635,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x98d07c005cea52102549964e374db87ed764bdb1840c7e4d0822a34701829208</t>
+          <t>0x8004902c8df50fb0691955c2dde204aa37aea6ffc9f11cb60795a2b8862e7e34</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -651,15 +643,19 @@
           <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>11.17999</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.3188</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -667,7 +663,11 @@
           <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>KF Drita -1.5</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -675,27 +675,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Riga FC vs Vardar</t>
+          <t>KF Drita vs Floriana</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Riga FC</t>
+          <t>KF Drita</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Floriana</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x3ce984b8d5a4fd077770e33c33bd5244077e868cb901d0b9544238e72630158d</t>
+          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19548393</t>
+          <t>L19556829</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785064821</t>
+          <t>1785065693</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785258000</t>
+          <t>1785261600</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>22.304219</t>
+          <t>5.301961</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,7 +747,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x90084d34df7f1c1dba6533a65ec3b370264b980f4ee2f405409784667aef3385</t>
+          <t>0x9d52e065d77a1e2ffa07fa7250522f55f6a20661ddb8ab22b3656a5e5f518751</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.3188</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785064821</t>
+          <t>1785065679</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>39.205882</t>
+          <t>9.003922</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,7 +859,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xd382b16331a33a8ef623d9f672b5567e3faaf5a8c56a6b1abbd17c5b3bf2447a</t>
+          <t>0xf072d053c048f056d7fa49c75da51e0772df0db003eaf3ddf341cb2fcc16c416</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -874,22 +874,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.3188</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>KF Drita -1.5</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -899,27 +899,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Riga FC vs Vardar</t>
+          <t>KF Drita vs Floriana</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Riga FC</t>
+          <t>KF Drita</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Floriana</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x3df545e9e324274c452d3611c5ff53dc80c8487fce47da81056d17c1b4257d63</t>
+          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19548393</t>
+          <t>L19556829</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -944,17 +944,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785064819</t>
+          <t>1785065519</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1785258000</t>
+          <t>1785261600</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>13.888889</t>
+          <t>14.117647</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,31 +971,39 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xc5ab66578686247686091622e73b8f1713617d5de6c2687bbf706bdd9a1c79eb</t>
+          <t>0xe1a18ecff833fc919588fdf2e22421fae16e5d31600f43cd14887e49499b233e</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x594542a29FFceEAeaDD2e67955437c928B51B758</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.2637</t>
+          <t>1.3325</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>KF Drita -1.5</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -1003,27 +1011,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Riga FC vs Vardar</t>
+          <t>KF Drita vs Floriana</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Riga FC</t>
+          <t>KF Drita</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Floriana</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x8f444d513fee4c89c59a5fac9732f2bdbc34c255f1e145e912b5e8d3864de79a</t>
+          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19548393</t>
+          <t>L19556829</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1048,17 +1056,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785064813</t>
+          <t>1785065131</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1785258000</t>
+          <t>1785261600</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>15.620853</t>
+          <t>9.052632</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1075,7 +1083,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x60648f843dfab3db80e7b11dc76bd422fb1242bf53219948830cbe4d1b29ee2e</t>
+          <t>0x97e956b7b7cfe7d56ae2e8711191f397ae89244a032e763798c4b0021c72d481</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1090,22 +1098,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.3325</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>KF Drita -1.5</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1115,27 +1123,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Riga FC vs Vardar</t>
+          <t>KF Drita vs Floriana</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Riga FC</t>
+          <t>KF Drita</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Floriana</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x3df545e9e324274c452d3611c5ff53dc80c8487fce47da81056d17c1b4257d63</t>
+          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19548393</t>
+          <t>L19556829</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1160,17 +1168,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785064792</t>
+          <t>1785065030</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1785258000</t>
+          <t>1785261600</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>15.444444</t>
+          <t>11.458647</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1187,31 +1195,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xd4092c9aa9c679f18a84f2d088ee1a8595762c53fd62d16b214a853eff1fde81</t>
+          <t>0x1b6d50b0b2f30b843c8afcdf1bdd77c807787389b518c0d0118f66c5c53154d1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x594542a29FFceEAeaDD2e67955437c928B51B758</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.2637</t>
+          <t>1.3325</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>KF Drita -1.5</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -1219,27 +1235,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Riga FC vs Vardar</t>
+          <t>KF Drita vs Floriana</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Riga FC</t>
+          <t>KF Drita</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Floriana</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x8f444d513fee4c89c59a5fac9732f2bdbc34c255f1e145e912b5e8d3864de79a</t>
+          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19548393</t>
+          <t>L19556829</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1264,17 +1280,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785064770</t>
+          <t>1785064974</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1785258000</t>
+          <t>1785261600</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>13.914692</t>
+          <t>3.007519</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1291,102 +1307,862 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>0x7de08a0243073e49c6e479dead7f166232ecd3480830513fb8953abf4d30f575</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Vardar</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Riga FC vs Vardar</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Riga FC</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Vardar</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0x3df545e9e324274c452d3611c5ff53dc80c8487fce47da81056d17c1b4257d63</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>L19548393</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>1785064838</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>1785258000</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>13.333333</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>0x98d07c005cea52102549964e374db87ed764bdb1840c7e4d0822a34701829208</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>11.17999</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1.5012</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Riga FC vs Vardar</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Riga FC</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Vardar</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0x3ce984b8d5a4fd077770e33c33bd5244077e868cb901d0b9544238e72630158d</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>L19548393</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>1785064821</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>1785258000</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>22.304219</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>0x90084d34df7f1c1dba6533a65ec3b370264b980f4ee2f405409784667aef3385</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>13.33</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>KF Drita -1.5</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>KF Drita vs Floriana</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>KF Drita</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Floriana</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>L19556829</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>1785064821</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>1785261600</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>39.205882</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>0xd382b16331a33a8ef623d9f672b5567e3faaf5a8c56a6b1abbd17c5b3bf2447a</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Vardar</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Riga FC vs Vardar</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Riga FC</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Vardar</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0x3df545e9e324274c452d3611c5ff53dc80c8487fce47da81056d17c1b4257d63</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>L19548393</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>1785064819</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>1785258000</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>13.888889</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>0xc5ab66578686247686091622e73b8f1713617d5de6c2687bbf706bdd9a1c79eb</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0x594542a29FFceEAeaDD2e67955437c928B51B758</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>4.12</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1.2637</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Riga FC vs Vardar</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Riga FC</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Vardar</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0x8f444d513fee4c89c59a5fac9732f2bdbc34c255f1e145e912b5e8d3864de79a</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>L19548393</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>1785064813</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>1785258000</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>15.620853</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>0x60648f843dfab3db80e7b11dc76bd422fb1242bf53219948830cbe4d1b29ee2e</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Vardar</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Riga FC vs Vardar</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Riga FC</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Vardar</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0x3df545e9e324274c452d3611c5ff53dc80c8487fce47da81056d17c1b4257d63</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>L19548393</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>1785064792</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>1785258000</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>15.444444</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>0xd4092c9aa9c679f18a84f2d088ee1a8595762c53fd62d16b214a853eff1fde81</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0x594542a29FFceEAeaDD2e67955437c928B51B758</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>3.67</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1.2637</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Riga FC vs Vardar</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Riga FC</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Vardar</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>0x8f444d513fee4c89c59a5fac9732f2bdbc34c255f1e145e912b5e8d3864de79a</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>L19548393</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1785064770</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1785258000</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>13.914692</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>0x3a9ab01f5b98d3619f0b7d9da475c1eabc0e13099a65941bdca6bd024e7991b6</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
         <is>
           <t>1.35</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>1.2637</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>Riga FC vs Vardar</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>Riga FC</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>Vardar</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>0x8f444d513fee4c89c59a5fac9732f2bdbc34c255f1e145e912b5e8d3864de79a</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>L19548393</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
         <is>
           <t>1785064754</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>1785258000</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>5.118483</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/UEFA Conference League/trades.xlsx
+++ b/data/sxbet/ligas/UEFA Conference League/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,59 +531,67 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xb86a834aa70af447f0675d386c1849b1c99fbb8415a4a0f57dedbfc3374369c8</t>
+          <t>0x00ae6c3a5ed7e25ed4adcc5d726b723762a6ddfb651274951dc984b567621eef</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>10.74</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.2875</t>
+          <t>1.1675</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Dukagjini</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>UEFA Conference League</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>UEFA Conference League</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>KF Drita vs Floriana</t>
+          <t>Dukagjini vs FC Lugano</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>KF Drita</t>
+          <t>Dukagjini</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Floriana</t>
+          <t>FC Lugano</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x74cee3640eed67802d8602418d415d7e5f881528425b4aded0a73b883c57f7c2</t>
+          <t>0xb4e6b34f8bd841e610d92a6e94ae60f508da52a98987521a70ab1ff92547c4a1</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19556829</t>
+          <t>L19578699</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785068425</t>
+          <t>1785164985</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785261600</t>
+          <t>1785335400</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>37.356522</t>
+          <t>10.859701</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,12 +643,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x8004902c8df50fb0691955c2dde204aa37aea6ffc9f11cb60795a2b8862e7e34</t>
+          <t>0x3d30d13f4f7532b8458d9fcb5fefaa11b7fdc084e05b8ea5921efdd1815c2b2e</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -650,22 +658,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.802</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.3188</t>
+          <t>1.1675</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>KF Drita -1.5</t>
+          <t>Dukagjini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -675,27 +683,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>KF Drita vs Floriana</t>
+          <t>Dukagjini vs FC Lugano</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>KF Drita</t>
+          <t>Dukagjini</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Floriana</t>
+          <t>FC Lugano</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
+          <t>0xb4e6b34f8bd841e610d92a6e94ae60f508da52a98987521a70ab1ff92547c4a1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19556829</t>
+          <t>L19578699</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -720,17 +728,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785065693</t>
+          <t>1785162974</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785261600</t>
+          <t>1785335400</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>5.301961</t>
+          <t>10.758209</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,39 +755,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x9d52e065d77a1e2ffa07fa7250522f55f6a20661ddb8ab22b3656a5e5f518751</t>
+          <t>0x79647a96f9215372245b4b53f196e63141ae86a1ea37ec3c520054924f339f07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.3188</t>
+          <t>1.2975</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>KF Drita -1.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -787,27 +787,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>KF Drita vs Floriana</t>
+          <t>Apollon Limassol FC vs FC Dila Gori</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>KF Drita</t>
+          <t>Apollon Limassol FC</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Floriana</t>
+          <t>FC Dila Gori</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
+          <t>0x000702f32390bc2acb841097855bbcf831db778647d8ef65ce0eb22695863bdc</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19556829</t>
+          <t>L19548403</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785065679</t>
+          <t>1785160034</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785261600</t>
+          <t>1785258000</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>9.003922</t>
+          <t>24.470588</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,12 +859,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xf072d053c048f056d7fa49c75da51e0772df0db003eaf3ddf341cb2fcc16c416</t>
+          <t>0xc738fb5ab6b1a30b7c6c1ec2cd7f70095001f6e7c404f7f168998f3ce0923565</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -874,22 +874,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>281.53996</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.3188</t>
+          <t>1.8588</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>UEFA Conference League</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>KF Drita -1.5</t>
+          <t>Apollon Limassol FC</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -899,27 +899,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>KF Drita vs Floriana</t>
+          <t>Apollon Limassol FC vs FC Dila Gori</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>KF Drita</t>
+          <t>Apollon Limassol FC</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Floriana</t>
+          <t>FC Dila Gori</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
+          <t>0x6b053f472a4306388af8fe5ea15275295a0aae1b19a9f51e5b3c924cb4aacd4d</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19556829</t>
+          <t>L19548403</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -944,17 +944,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785065519</t>
+          <t>1785159837</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1785261600</t>
+          <t>1785258000</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>14.117647</t>
+          <t>327.848571</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,7 +971,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xe1a18ecff833fc919588fdf2e22421fae16e5d31600f43cd14887e49499b233e</t>
+          <t>0x0b99d0d305609060f8495bfe5f8c95e1a0b399ad11cc9adf4f34153f68c97d71</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -986,22 +986,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.3325</t>
+          <t>1.1025</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>KF Drita -1.5</t>
+          <t>FC Dila Gori</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1011,27 +1011,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>KF Drita vs Floriana</t>
+          <t>Apollon Limassol FC vs FC Dila Gori</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>KF Drita</t>
+          <t>Apollon Limassol FC</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Floriana</t>
+          <t>FC Dila Gori</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
+          <t>0x66b17a5927b2a92224c605c32e8306f8dc8fabb6ccff81abfc5fbafb709f9a22</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19556829</t>
+          <t>L19548403</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1056,17 +1056,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785065131</t>
+          <t>1785143243</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1785261600</t>
+          <t>1785258000</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>9.052632</t>
+          <t>9.853659</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x97e956b7b7cfe7d56ae2e8711191f397ae89244a032e763798c4b0021c72d481</t>
+          <t>0xa2274ee0f4684479f0988ac6a5139708014cf026476c7cf9b37b3a416e7b5747</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x1b1185C2A2d1Ec3CA592f5c21f52dD4aD449163f</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1098,22 +1098,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.3325</t>
+          <t>1.0625</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>KF Drita -1.5</t>
+          <t>Paide Linnameeskond</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1123,27 +1123,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>KF Drita vs Floriana</t>
+          <t>Zira FK vs Paide Linnameeskond</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>KF Drita</t>
+          <t>Zira FK</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Floriana</t>
+          <t>Paide Linnameeskond</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
+          <t>0xc2274f3d5306fe3b7bf272b7cfce16894bf01595fd8fa3181858809c5afd887d</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19556829</t>
+          <t>L19568228</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1168,17 +1168,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785065030</t>
+          <t>1785123628</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1785261600</t>
+          <t>1785427200</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>11.458647</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1195,7 +1195,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x1b6d50b0b2f30b843c8afcdf1bdd77c807787389b518c0d0118f66c5c53154d1</t>
+          <t>0x4b249266f4a129a90a4f4289f80efd22864a0b55a615a30c01a744c9e6fa007e</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1210,22 +1210,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.3325</t>
+          <t>1.2463</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>KF Drita -1.5</t>
+          <t>FC Spartak Trnava</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1235,27 +1235,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>KF Drita vs Floriana</t>
+          <t>FC CSKA Sofia 1948 vs FC Spartak Trnava</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>KF Drita</t>
+          <t>FC CSKA Sofia 1948</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Floriana</t>
+          <t>FC Spartak Trnava</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
+          <t>0xe6d3ed6a25306fb2793f56682ed261dbde83f239772758b37aeecc6a973830a6</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19556829</t>
+          <t>L19548391</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1280,17 +1280,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785064974</t>
+          <t>1785114331</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1785261600</t>
+          <t>1785259800</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>3.007519</t>
+          <t>20.020305</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1307,27 +1307,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x7de08a0243073e49c6e479dead7f166232ecd3480830513fb8953abf4d30f575</t>
+          <t>0xbcaacd1e8dc7d60abd70f28c7ffba7450e4c76519b53d45633047b2e308ce8df</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.835</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1335,11 +1331,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Vardar</t>
-        </is>
-      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -1347,27 +1339,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Riga FC vs Vardar</t>
+          <t>Dukagjini vs FC Lugano</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Riga FC</t>
+          <t>Dukagjini</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>FC Lugano</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x3df545e9e324274c452d3611c5ff53dc80c8487fce47da81056d17c1b4257d63</t>
+          <t>0xb4e6b34f8bd841e610d92a6e94ae60f508da52a98987521a70ab1ff92547c4a1</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19548393</t>
+          <t>L19578699</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1392,17 +1384,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785064838</t>
+          <t>1785108140</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1785258000</t>
+          <t>1785335400</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>13.333333</t>
+          <t>5.02994</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1419,28 +1411,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x98d07c005cea52102549964e374db87ed764bdb1840c7e4d0822a34701829208</t>
+          <t>0xc4f834cac0960a0d1d3dfd961f4ed03d26a908325b0613bbc25d8271e7ea9596</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>11.17999</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.4062</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1451,27 +1443,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Riga FC vs Vardar</t>
+          <t>KF Drita vs Floriana</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Riga FC</t>
+          <t>KF Drita</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Floriana</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x3ce984b8d5a4fd077770e33c33bd5244077e868cb901d0b9544238e72630158d</t>
+          <t>0xd80db7f29b1a9bf7479fe759db5892459ba76d2573c8028c682ca72ca26fa563</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19548393</t>
+          <t>L19556829</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1496,17 +1488,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785064821</t>
+          <t>1785102921</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1785258000</t>
+          <t>1785261600</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>22.304219</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1523,12 +1515,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x90084d34df7f1c1dba6533a65ec3b370264b980f4ee2f405409784667aef3385</t>
+          <t>0x642cead4cce6abf15e60b5f101292963653928af192a53d61cf13be1f5735346</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1538,22 +1530,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>25.11</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Asian Handicap (-2.5)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>KF Drita -1.5</t>
+          <t>SK Rapid Wien -2.5</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1563,27 +1555,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>KF Drita vs Floriana</t>
+          <t>SK Rapid Wien vs FC Santa Coloma</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>KF Drita</t>
+          <t>SK Rapid Wien</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Floriana</t>
+          <t>FC Santa Coloma</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
+          <t>0x568429d159b17f3e17f83384554dcb4508d96942d411a493bfcdd9af2fd2df07</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19556829</t>
+          <t>L19558557</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1608,17 +1600,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785064821</t>
+          <t>1785100795</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1785261600</t>
+          <t>1785349800</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>39.205882</t>
+          <t>51.773196</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1635,39 +1627,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xd382b16331a33a8ef623d9f672b5567e3faaf5a8c56a6b1abbd17c5b3bf2447a</t>
+          <t>0xb86a834aa70af447f0675d386c1849b1c99fbb8415a4a0f57dedbfc3374369c8</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>10.74</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.2875</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Vardar</t>
-        </is>
-      </c>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -1675,27 +1659,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Riga FC vs Vardar</t>
+          <t>KF Drita vs Floriana</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Riga FC</t>
+          <t>KF Drita</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Floriana</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x3df545e9e324274c452d3611c5ff53dc80c8487fce47da81056d17c1b4257d63</t>
+          <t>0x74cee3640eed67802d8602418d415d7e5f881528425b4aded0a73b883c57f7c2</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19548393</t>
+          <t>L19556829</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1720,17 +1704,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785064819</t>
+          <t>1785068425</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1785258000</t>
+          <t>1785261600</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>13.888889</t>
+          <t>37.356522</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1747,31 +1731,39 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xc5ab66578686247686091622e73b8f1713617d5de6c2687bbf706bdd9a1c79eb</t>
+          <t>0x8004902c8df50fb0691955c2dde204aa37aea6ffc9f11cb60795a2b8862e7e34</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x594542a29FFceEAeaDD2e67955437c928B51B758</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.2637</t>
+          <t>1.3188</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>KF Drita -1.5</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -1779,27 +1771,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Riga FC vs Vardar</t>
+          <t>KF Drita vs Floriana</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Riga FC</t>
+          <t>KF Drita</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Floriana</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x8f444d513fee4c89c59a5fac9732f2bdbc34c255f1e145e912b5e8d3864de79a</t>
+          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19548393</t>
+          <t>L19556829</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1824,17 +1816,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785064813</t>
+          <t>1785065693</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1785258000</t>
+          <t>1785261600</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>15.620853</t>
+          <t>5.301961</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1851,7 +1843,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x60648f843dfab3db80e7b11dc76bd422fb1242bf53219948830cbe4d1b29ee2e</t>
+          <t>0x9d52e065d77a1e2ffa07fa7250522f55f6a20661ddb8ab22b3656a5e5f518751</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1866,22 +1858,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.3188</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>KF Drita -1.5</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1891,27 +1883,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Riga FC vs Vardar</t>
+          <t>KF Drita vs Floriana</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Riga FC</t>
+          <t>KF Drita</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Floriana</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x3df545e9e324274c452d3611c5ff53dc80c8487fce47da81056d17c1b4257d63</t>
+          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19548393</t>
+          <t>L19556829</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1936,17 +1928,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785064792</t>
+          <t>1785065679</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1785258000</t>
+          <t>1785261600</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>15.444444</t>
+          <t>9.003922</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1963,31 +1955,39 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xd4092c9aa9c679f18a84f2d088ee1a8595762c53fd62d16b214a853eff1fde81</t>
+          <t>0xf072d053c048f056d7fa49c75da51e0772df0db003eaf3ddf341cb2fcc16c416</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x594542a29FFceEAeaDD2e67955437c928B51B758</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.2637</t>
+          <t>1.3188</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>KF Drita -1.5</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -1995,27 +1995,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Riga FC vs Vardar</t>
+          <t>KF Drita vs Floriana</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Riga FC</t>
+          <t>KF Drita</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Floriana</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x8f444d513fee4c89c59a5fac9732f2bdbc34c255f1e145e912b5e8d3864de79a</t>
+          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19548393</t>
+          <t>L19556829</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2040,17 +2040,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785064770</t>
+          <t>1785065519</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1785258000</t>
+          <t>1785261600</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>13.914692</t>
+          <t>14.117647</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2067,102 +2067,1198 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>0xe1a18ecff833fc919588fdf2e22421fae16e5d31600f43cd14887e49499b233e</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>3.01</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1.3325</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>KF Drita -1.5</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>KF Drita vs Floriana</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>KF Drita</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Floriana</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>L19556829</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>1785065131</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>1785261600</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>9.052632</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>0x97e956b7b7cfe7d56ae2e8711191f397ae89244a032e763798c4b0021c72d481</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>3.81</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1.3325</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KF Drita -1.5</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>KF Drita vs Floriana</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>KF Drita</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Floriana</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>L19556829</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>1785065030</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>1785261600</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>11.458647</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>0x1b6d50b0b2f30b843c8afcdf1bdd77c807787389b518c0d0118f66c5c53154d1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1.3325</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KF Drita -1.5</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>KF Drita vs Floriana</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>KF Drita</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Floriana</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>L19556829</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>1785064974</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>1785261600</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>3.007519</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>0x7de08a0243073e49c6e479dead7f166232ecd3480830513fb8953abf4d30f575</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Vardar</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Riga FC vs Vardar</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Riga FC</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Vardar</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0x3df545e9e324274c452d3611c5ff53dc80c8487fce47da81056d17c1b4257d63</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>L19548393</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>1785064838</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>1785258000</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>13.333333</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>0x98d07c005cea52102549964e374db87ed764bdb1840c7e4d0822a34701829208</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>11.17999</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1.5012</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Riga FC vs Vardar</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Riga FC</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Vardar</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0x3ce984b8d5a4fd077770e33c33bd5244077e868cb901d0b9544238e72630158d</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>L19548393</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1785064821</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1785258000</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>22.304219</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>0x90084d34df7f1c1dba6533a65ec3b370264b980f4ee2f405409784667aef3385</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>13.33</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>KF Drita -1.5</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>KF Drita vs Floriana</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>KF Drita</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Floriana</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>L19556829</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>1785064821</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>1785261600</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>39.205882</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>0xd382b16331a33a8ef623d9f672b5567e3faaf5a8c56a6b1abbd17c5b3bf2447a</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Vardar</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Riga FC vs Vardar</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Riga FC</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Vardar</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>0x3df545e9e324274c452d3611c5ff53dc80c8487fce47da81056d17c1b4257d63</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>L19548393</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>1785064819</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>1785258000</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>13.888889</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>0xc5ab66578686247686091622e73b8f1713617d5de6c2687bbf706bdd9a1c79eb</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0x594542a29FFceEAeaDD2e67955437c928B51B758</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>4.12</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1.2637</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Riga FC vs Vardar</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Riga FC</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Vardar</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>0x8f444d513fee4c89c59a5fac9732f2bdbc34c255f1e145e912b5e8d3864de79a</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>L19548393</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>1785064813</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>1785258000</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>15.620853</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>0x60648f843dfab3db80e7b11dc76bd422fb1242bf53219948830cbe4d1b29ee2e</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Vardar</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Riga FC vs Vardar</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Riga FC</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Vardar</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>0x3df545e9e324274c452d3611c5ff53dc80c8487fce47da81056d17c1b4257d63</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>L19548393</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>1785064792</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>1785258000</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>15.444444</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>0xd4092c9aa9c679f18a84f2d088ee1a8595762c53fd62d16b214a853eff1fde81</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0x594542a29FFceEAeaDD2e67955437c928B51B758</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>3.67</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1.2637</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Riga FC vs Vardar</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Riga FC</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Vardar</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>0x8f444d513fee4c89c59a5fac9732f2bdbc34c255f1e145e912b5e8d3864de79a</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>L19548393</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>1785064770</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>1785258000</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>13.914692</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>0x3a9ab01f5b98d3619f0b7d9da475c1eabc0e13099a65941bdca6bd024e7991b6</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
         <is>
           <t>1.35</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>1.2637</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr">
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>Riga FC vs Vardar</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>Riga FC</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>Vardar</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>0x8f444d513fee4c89c59a5fac9732f2bdbc34c255f1e145e912b5e8d3864de79a</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>L19548393</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
         <is>
           <t>1785064754</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>1785258000</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>5.118483</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/UEFA Conference League/trades.xlsx
+++ b/data/sxbet/ligas/UEFA Conference League/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V26"/>
+  <dimension ref="A1:V43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x00ae6c3a5ed7e25ed4adcc5d726b723762a6ddfb651274951dc984b567621eef</t>
+          <t>0xc2aab73ddffd7075b0f7b62fe496b81e8ff26c527fc6f8f306a4e978d3ed1efd</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
+          <t>0x155C76202e45BE70c50bfeD7eAeA3B98e7716Ff7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,12 +546,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.99999</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.1675</t>
+          <t>1.7437</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -561,7 +561,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dukagjini</t>
+          <t>Riga FC</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -571,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Dukagjini vs FC Lugano</t>
+          <t>Riga FC vs Vardar</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Dukagjini</t>
+          <t>Riga FC</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>FC Lugano</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xb4e6b34f8bd841e610d92a6e94ae60f508da52a98987521a70ab1ff92547c4a1</t>
+          <t>0x8f444d513fee4c89c59a5fac9732f2bdbc34c255f1e145e912b5e8d3864de79a</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19578699</t>
+          <t>L19548393</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785164985</t>
+          <t>1785188484</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785335400</t>
+          <t>1785258000</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>10.859701</t>
+          <t>2.689062</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,12 +643,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x3d30d13f4f7532b8458d9fcb5fefaa11b7fdc084e05b8ea5921efdd1815c2b2e</t>
+          <t>0x145c09d9142ba2cbced4c8388017e78e14aa9401ee12d36d8129500f13df032e</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -658,22 +658,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.802</t>
+          <t>54.69828</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.1675</t>
+          <t>1.5288</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dukagjini</t>
+          <t>KF Drita -1</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -683,27 +683,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Dukagjini vs FC Lugano</t>
+          <t>KF Drita vs Floriana</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Dukagjini</t>
+          <t>KF Drita</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>FC Lugano</t>
+          <t>Floriana</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xb4e6b34f8bd841e610d92a6e94ae60f508da52a98987521a70ab1ff92547c4a1</t>
+          <t>0x5412f1c6d1dfb833bab11103f4cc8d7e6df53302c4951b2ac6b6bec4e6f5ef02</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19578699</t>
+          <t>L19556829</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -728,17 +728,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785162974</t>
+          <t>1785188240</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785335400</t>
+          <t>1785261600</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>10.758209</t>
+          <t>103.448284</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,31 +755,39 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x79647a96f9215372245b4b53f196e63141ae86a1ea37ec3c520054924f339f07</t>
+          <t>0x9cf4023491039f5bb7dac0df23c846094dd01f9dbee02e57798e16c37d85f644</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.2975</t>
+          <t>1.395</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -787,27 +795,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Apollon Limassol FC vs FC Dila Gori</t>
+          <t>Riga FC vs Vardar</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Apollon Limassol FC</t>
+          <t>Riga FC</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>FC Dila Gori</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x000702f32390bc2acb841097855bbcf831db778647d8ef65ce0eb22695863bdc</t>
+          <t>0x4b27547b8aa1ca6be4f6c92d7d7529a6f2db813e76b6e813d964bae73b66325b</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19548403</t>
+          <t>L19548393</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -832,7 +840,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785160034</t>
+          <t>1785187553</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -842,7 +850,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>24.470588</t>
+          <t>6.708861</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,12 +867,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xc738fb5ab6b1a30b7c6c1ec2cd7f70095001f6e7c404f7f168998f3ce0923565</t>
+          <t>0xc7e6d7d15508ccc8392a870d6681e7b64fd2e6038be310a8a884315b6a1c961c</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
+          <t>0x1b1185C2A2d1Ec3CA592f5c21f52dD4aD449163f</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -874,52 +882,52 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>281.53996</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.8588</t>
+          <t>1.175</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>UEFA Conference League</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Apollon Limassol FC</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>UEFA Conference League</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Apollon Limassol FC vs FC Dila Gori</t>
+          <t>Riga FC vs Vardar</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Apollon Limassol FC</t>
+          <t>Riga FC</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>FC Dila Gori</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x6b053f472a4306388af8fe5ea15275295a0aae1b19a9f51e5b3c924cb4aacd4d</t>
+          <t>0x493fb5a9e01ebf84f758d2393d26a55e30244a3f9d8b15eb25d6f79450841850</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19548403</t>
+          <t>L19548393</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -944,7 +952,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785159837</t>
+          <t>1785186255</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -954,7 +962,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>327.848571</t>
+          <t>142.857143</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,12 +979,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x0b99d0d305609060f8495bfe5f8c95e1a0b399ad11cc9adf4f34153f68c97d71</t>
+          <t>0x97bc06ccc193bcef116dbd3167a750fb9715b73503439c03d33582d95f59a027</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x1b1185C2A2d1Ec3CA592f5c21f52dD4aD449163f</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -986,12 +994,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.1025</t>
+          <t>1.1125</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1056,7 +1064,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785143243</t>
+          <t>1785186085</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1066,7 +1074,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>9.853659</t>
+          <t>222.222222</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1083,27 +1091,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xa2274ee0f4684479f0988ac6a5139708014cf026476c7cf9b37b3a416e7b5747</t>
+          <t>0xa1b38b181df840d94fccfceb9be5cfd1c9808b3603eb40e8e856fea5c36c33f0</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x1b1185C2A2d1Ec3CA592f5c21f52dD4aD449163f</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.0625</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1111,11 +1115,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Paide Linnameeskond</t>
-        </is>
-      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -1123,27 +1123,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Zira FK vs Paide Linnameeskond</t>
+          <t>GKS Katowice vs MSK Zilina</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Zira FK</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Paide Linnameeskond</t>
+          <t>MSK Zilina</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xc2274f3d5306fe3b7bf272b7cfce16894bf01595fd8fa3181858809c5afd887d</t>
+          <t>0x17ea810aed80a43d53397b03233a18bc09fd2fccf8db1130f11e12f7f95c91e7</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19568228</t>
+          <t>L19568244</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1168,17 +1168,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785123628</t>
+          <t>1785184086</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1785427200</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1195,12 +1195,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x4b249266f4a129a90a4f4289f80efd22864a0b55a615a30c01a744c9e6fa007e</t>
+          <t>0xe5723419c39bca85b784eb615a725a9a26a5c239d525f82b27535463ba9d9f88</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1210,22 +1210,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>203.62057</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.2463</t>
+          <t>1.8838</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>UEFA Conference League</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>FC Spartak Trnava</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1235,27 +1235,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>FC CSKA Sofia 1948 vs FC Spartak Trnava</t>
+          <t>Panathinaikos vs Paksi SE</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>FC CSKA Sofia 1948</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>FC Spartak Trnava</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xe6d3ed6a25306fb2793f56682ed261dbde83f239772758b37aeecc6a973830a6</t>
+          <t>0x9747c98c82c1e1aeebd441f71649b575a324218f5bb412402cb90fb1639eb40f</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19548391</t>
+          <t>L19568307</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1280,17 +1280,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785114331</t>
+          <t>1785178979</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1785259800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>20.020305</t>
+          <t>230.405171</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1307,28 +1307,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xbcaacd1e8dc7d60abd70f28c7ffba7450e4c76519b53d45633047b2e308ce8df</t>
+          <t>0x9d2c4725405077ca1bceaff142e2ed3d4e9ff5d3b138a2f49b31afb87c9fa625</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>25.92059</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.835</t>
+          <t>1.1125</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>UEFA Conference League</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1339,27 +1339,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Dukagjini vs FC Lugano</t>
+          <t>Panathinaikos vs Paksi SE</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Dukagjini</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>FC Lugano</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xb4e6b34f8bd841e610d92a6e94ae60f508da52a98987521a70ab1ff92547c4a1</t>
+          <t>0x9747c98c82c1e1aeebd441f71649b575a324218f5bb412402cb90fb1639eb40f</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19578699</t>
+          <t>L19568307</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1384,17 +1384,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785108140</t>
+          <t>1785178979</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1785335400</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>5.02994</t>
+          <t>230.405244</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1411,31 +1411,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xc4f834cac0960a0d1d3dfd961f4ed03d26a908325b0613bbc25d8271e7ea9596</t>
+          <t>0x09e55e9944cfa459297c6a9f1bd507159b106de1f3987c8394a2b0fd67f3ba3b</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>82.92</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.4062</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>FC CSKA Sofia 1948</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -1443,27 +1451,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>KF Drita vs Floriana</t>
+          <t>FC CSKA Sofia 1948 vs FC Spartak Trnava</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>KF Drita</t>
+          <t>FC CSKA Sofia 1948</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Floriana</t>
+          <t>FC Spartak Trnava</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xd80db7f29b1a9bf7479fe759db5892459ba76d2573c8028c682ca72ca26fa563</t>
+          <t>0x0f0e918dc732446e9ce6f03b0a5b34d1a075bcff9ed3e2ca33563b8eea52d345</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19556829</t>
+          <t>L19548391</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1488,17 +1496,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785102921</t>
+          <t>1785178520</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1785261600</t>
+          <t>1785259800</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>123.761194</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1515,12 +1523,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x642cead4cce6abf15e60b5f101292963653928af192a53d61cf13be1f5735346</t>
+          <t>0xff24d53e0d12e00d437b591e035e6a102c9ec294448637ea1d827288ccdfd669</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1530,22 +1538,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>25.11</t>
+          <t>32.29</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.7025</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
+          <t>UEFA Conference League</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SK Rapid Wien -2.5</t>
+          <t>FC CSKA Sofia 1948</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1555,27 +1563,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>SK Rapid Wien vs FC Santa Coloma</t>
+          <t>FC CSKA Sofia 1948 vs FC Spartak Trnava</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>SK Rapid Wien</t>
+          <t>FC CSKA Sofia 1948</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>FC Santa Coloma</t>
+          <t>FC Spartak Trnava</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x568429d159b17f3e17f83384554dcb4508d96942d411a493bfcdd9af2fd2df07</t>
+          <t>0x0f0e918dc732446e9ce6f03b0a5b34d1a075bcff9ed3e2ca33563b8eea52d345</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19558557</t>
+          <t>L19548391</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1600,17 +1608,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785100795</t>
+          <t>1785178483</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1785349800</t>
+          <t>1785259800</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>51.773196</t>
+          <t>45.964413</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1627,28 +1635,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xb86a834aa70af447f0675d386c1849b1c99fbb8415a4a0f57dedbfc3374369c8</t>
+          <t>0xa2145f7f39e67fd641cdc795fb35638f93441f575672f474dcbb129d212b2071</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>10.74</t>
+          <t>282.04998</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.2875</t>
+          <t>1.8675</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>UEFA Conference League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1674,7 +1682,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x74cee3640eed67802d8602418d415d7e5f881528425b4aded0a73b883c57f7c2</t>
+          <t>0xd67d116960d6336d573e0df6e68fbc4925de62b55e56c443ceca3b50f83a0f30</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1704,7 +1712,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785068425</t>
+          <t>1785178247</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1714,7 +1722,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>37.356522</t>
+          <t>325.12966</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1731,12 +1739,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x8004902c8df50fb0691955c2dde204aa37aea6ffc9f11cb60795a2b8862e7e34</t>
+          <t>0x81f3111a3468acf1de52d30ac0604c9ee06fc1a0787546268f23addd010feff2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1746,22 +1754,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>101.96</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.3188</t>
+          <t>1.8013</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>UEFA Conference League</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>KF Drita -1.5</t>
+          <t>KF Drita</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1786,7 +1794,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
+          <t>0x09c0b1c15b6ea28d2c0107f466fade6e9caf4c75d4f55998d43c1e51232e5234</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1816,7 +1824,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785065693</t>
+          <t>1785175205</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1826,7 +1834,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>5.301961</t>
+          <t>127.25117</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1843,12 +1851,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x9d52e065d77a1e2ffa07fa7250522f55f6a20661ddb8ab22b3656a5e5f518751</t>
+          <t>0xe051c5dca29cf389a307215b76298a2e45bf4baccb56422aafc9a3c300c155dd</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1858,22 +1866,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>18.61997</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.3188</t>
+          <t>1.8013</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>UEFA Conference League</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>KF Drita -1.5</t>
+          <t>KF Drita</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1898,7 +1906,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
+          <t>0x09c0b1c15b6ea28d2c0107f466fade6e9caf4c75d4f55998d43c1e51232e5234</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1928,7 +1936,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785065679</t>
+          <t>1785174328</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1938,7 +1946,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>9.003922</t>
+          <t>23.238652</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1955,12 +1963,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xf072d053c048f056d7fa49c75da51e0772df0db003eaf3ddf341cb2fcc16c416</t>
+          <t>0xdaaf4df1704b396668995377988eea9bc6831ef12573030f333c949030199143</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1970,22 +1978,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>21.48999</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.3188</t>
+          <t>1.8013</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>UEFA Conference League</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>KF Drita -1.5</t>
+          <t>KF Drita</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2010,7 +2018,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
+          <t>0x09c0b1c15b6ea28d2c0107f466fade6e9caf4c75d4f55998d43c1e51232e5234</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2040,7 +2048,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785065519</t>
+          <t>1785174135</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2050,7 +2058,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>14.117647</t>
+          <t>26.82058</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2067,27 +2075,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xe1a18ecff833fc919588fdf2e22421fae16e5d31600f43cd14887e49499b233e</t>
+          <t>0x94f8a12cc97509762210745df2b56516620b6491bd6d10909e3496335a55dd21</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x960070fC76573ff9c086dB473f99CA99ea914dd6</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.3325</t>
+          <t>1.6225</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2095,11 +2099,7 @@
           <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>KF Drita -1.5</t>
-        </is>
-      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785065131</t>
+          <t>1785172928</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>9.052632</t>
+          <t>20.883534</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2179,12 +2179,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x97e956b7b7cfe7d56ae2e8711191f397ae89244a032e763798c4b0021c72d481</t>
+          <t>0x0f77d19b1a11d1f8146d9103f3be3cbc4c3ff95c3bafe707daeb72cd0f7580ae</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2194,22 +2194,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>16.67997</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.3325</t>
+          <t>1.815</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>UEFA Conference League</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>KF Drita -1.5</t>
+          <t>KF Drita</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
+          <t>0x09c0b1c15b6ea28d2c0107f466fade6e9caf4c75d4f55998d43c1e51232e5234</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785065030</t>
+          <t>1785172335</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>11.458647</t>
+          <t>20.466221</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2291,39 +2291,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x1b6d50b0b2f30b843c8afcdf1bdd77c807787389b518c0d0118f66c5c53154d1</t>
+          <t>0x5e2fb7a1e61868dc87b64881470b8319cd876087d156626150e830a7cf27d189</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.3325</t>
+          <t>1.285</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>KF Drita -1.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -2331,27 +2323,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>KF Drita vs Floriana</t>
+          <t>Apollon Limassol FC vs FC Dila Gori</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>KF Drita</t>
+          <t>Apollon Limassol FC</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Floriana</t>
+          <t>FC Dila Gori</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
+          <t>0x000702f32390bc2acb841097855bbcf831db778647d8ef65ce0eb22695863bdc</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19556829</t>
+          <t>L19548403</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2376,17 +2368,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785064974</t>
+          <t>1785171495</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1785261600</t>
+          <t>1785258000</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>3.007519</t>
+          <t>294.035088</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2403,12 +2395,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x7de08a0243073e49c6e479dead7f166232ecd3480830513fb8953abf4d30f575</t>
+          <t>0x00ae6c3a5ed7e25ed4adcc5d726b723762a6ddfb651274951dc984b567621eef</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2418,12 +2410,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.1675</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2433,7 +2425,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Dukagjini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2443,27 +2435,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Riga FC vs Vardar</t>
+          <t>Dukagjini vs FC Lugano</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Riga FC</t>
+          <t>Dukagjini</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>FC Lugano</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x3df545e9e324274c452d3611c5ff53dc80c8487fce47da81056d17c1b4257d63</t>
+          <t>0xb4e6b34f8bd841e610d92a6e94ae60f508da52a98987521a70ab1ff92547c4a1</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19548393</t>
+          <t>L19578699</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2488,17 +2480,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785064838</t>
+          <t>1785164985</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1785258000</t>
+          <t>1785335400</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>13.333333</t>
+          <t>10.859701</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2515,31 +2507,39 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x98d07c005cea52102549964e374db87ed764bdb1840c7e4d0822a34701829208</t>
+          <t>0x3d30d13f4f7532b8458d9fcb5fefaa11b7fdc084e05b8ea5921efdd1815c2b2e</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>11.17999</t>
+          <t>1.802</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.1675</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dukagjini</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -2547,27 +2547,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Riga FC vs Vardar</t>
+          <t>Dukagjini vs FC Lugano</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Riga FC</t>
+          <t>Dukagjini</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>FC Lugano</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x3ce984b8d5a4fd077770e33c33bd5244077e868cb901d0b9544238e72630158d</t>
+          <t>0xb4e6b34f8bd841e610d92a6e94ae60f508da52a98987521a70ab1ff92547c4a1</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19548393</t>
+          <t>L19578699</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2592,17 +2592,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785064821</t>
+          <t>1785162974</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1785258000</t>
+          <t>1785335400</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>22.304219</t>
+          <t>10.758209</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2619,39 +2619,31 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x90084d34df7f1c1dba6533a65ec3b370264b980f4ee2f405409784667aef3385</t>
+          <t>0x79647a96f9215372245b4b53f196e63141ae86a1ea37ec3c520054924f339f07</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.2975</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>KF Drita -1.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -2659,27 +2651,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>KF Drita vs Floriana</t>
+          <t>Apollon Limassol FC vs FC Dila Gori</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>KF Drita</t>
+          <t>Apollon Limassol FC</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Floriana</t>
+          <t>FC Dila Gori</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
+          <t>0x000702f32390bc2acb841097855bbcf831db778647d8ef65ce0eb22695863bdc</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19556829</t>
+          <t>L19548403</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2704,17 +2696,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785064821</t>
+          <t>1785160034</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1785261600</t>
+          <t>1785258000</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>39.205882</t>
+          <t>24.470588</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2731,12 +2723,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xd382b16331a33a8ef623d9f672b5567e3faaf5a8c56a6b1abbd17c5b3bf2447a</t>
+          <t>0xc738fb5ab6b1a30b7c6c1ec2cd7f70095001f6e7c404f7f168998f3ce0923565</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2746,22 +2738,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>281.53996</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.8588</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>UEFA Conference League</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Apollon Limassol FC</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2771,27 +2763,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Riga FC vs Vardar</t>
+          <t>Apollon Limassol FC vs FC Dila Gori</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Riga FC</t>
+          <t>Apollon Limassol FC</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>FC Dila Gori</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x3df545e9e324274c452d3611c5ff53dc80c8487fce47da81056d17c1b4257d63</t>
+          <t>0x6b053f472a4306388af8fe5ea15275295a0aae1b19a9f51e5b3c924cb4aacd4d</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19548393</t>
+          <t>L19548403</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2816,7 +2808,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785064819</t>
+          <t>1785159837</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2826,7 +2818,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>13.888889</t>
+          <t>327.848571</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2843,23 +2835,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xc5ab66578686247686091622e73b8f1713617d5de6c2687bbf706bdd9a1c79eb</t>
+          <t>0x0b99d0d305609060f8495bfe5f8c95e1a0b399ad11cc9adf4f34153f68c97d71</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x594542a29FFceEAeaDD2e67955437c928B51B758</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.2637</t>
+          <t>1.1025</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2867,7 +2863,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>FC Dila Gori</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -2875,27 +2875,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Riga FC vs Vardar</t>
+          <t>Apollon Limassol FC vs FC Dila Gori</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Riga FC</t>
+          <t>Apollon Limassol FC</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>FC Dila Gori</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x8f444d513fee4c89c59a5fac9732f2bdbc34c255f1e145e912b5e8d3864de79a</t>
+          <t>0x66b17a5927b2a92224c605c32e8306f8dc8fabb6ccff81abfc5fbafb709f9a22</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19548393</t>
+          <t>L19548403</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785064813</t>
+          <t>1785143243</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>15.620853</t>
+          <t>9.853659</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2947,12 +2947,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x60648f843dfab3db80e7b11dc76bd422fb1242bf53219948830cbe4d1b29ee2e</t>
+          <t>0xa2274ee0f4684479f0988ac6a5139708014cf026476c7cf9b37b3a416e7b5747</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x1b1185C2A2d1Ec3CA592f5c21f52dD4aD449163f</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.0625</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Paide Linnameeskond</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2987,27 +2987,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Riga FC vs Vardar</t>
+          <t>Zira FK vs Paide Linnameeskond</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Riga FC</t>
+          <t>Zira FK</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Paide Linnameeskond</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x3df545e9e324274c452d3611c5ff53dc80c8487fce47da81056d17c1b4257d63</t>
+          <t>0xc2274f3d5306fe3b7bf272b7cfce16894bf01595fd8fa3181858809c5afd887d</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19548393</t>
+          <t>L19568228</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3032,17 +3032,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785064792</t>
+          <t>1785123628</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1785258000</t>
+          <t>1785427200</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>15.444444</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3059,23 +3059,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0xd4092c9aa9c679f18a84f2d088ee1a8595762c53fd62d16b214a853eff1fde81</t>
+          <t>0x4b249266f4a129a90a4f4289f80efd22864a0b55a615a30c01a744c9e6fa007e</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x594542a29FFceEAeaDD2e67955437c928B51B758</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.2637</t>
+          <t>1.2463</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3083,7 +3087,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>FC Spartak Trnava</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -3091,27 +3099,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Riga FC vs Vardar</t>
+          <t>FC CSKA Sofia 1948 vs FC Spartak Trnava</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Riga FC</t>
+          <t>FC CSKA Sofia 1948</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>FC Spartak Trnava</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x8f444d513fee4c89c59a5fac9732f2bdbc34c255f1e145e912b5e8d3864de79a</t>
+          <t>0xe6d3ed6a25306fb2793f56682ed261dbde83f239772758b37aeecc6a973830a6</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19548393</t>
+          <t>L19548391</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3136,17 +3144,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785064770</t>
+          <t>1785114331</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1785258000</t>
+          <t>1785259800</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>13.914692</t>
+          <t>20.020305</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3163,7 +3171,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x3a9ab01f5b98d3619f0b7d9da475c1eabc0e13099a65941bdca6bd024e7991b6</t>
+          <t>0xbcaacd1e8dc7d60abd70f28c7ffba7450e4c76519b53d45633047b2e308ce8df</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3174,12 +3182,12 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.2637</t>
+          <t>1.835</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3195,70 +3203,1926 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
+          <t>Dukagjini vs FC Lugano</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Dukagjini</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>FC Lugano</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>0xb4e6b34f8bd841e610d92a6e94ae60f508da52a98987521a70ab1ff92547c4a1</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>L19578699</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>1785108140</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>1785335400</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>5.02994</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>0xc4f834cac0960a0d1d3dfd961f4ed03d26a908325b0613bbc25d8271e7ea9596</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>16.9</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1.4062</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>KF Drita vs Floriana</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>KF Drita</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Floriana</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>0xd80db7f29b1a9bf7479fe759db5892459ba76d2573c8028c682ca72ca26fa563</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>L19556829</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>1785102921</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>1785261600</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>41.6</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>0x642cead4cce6abf15e60b5f101292963653928af192a53d61cf13be1f5735346</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>25.11</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1.485</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>SK Rapid Wien -2.5</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>SK Rapid Wien vs FC Santa Coloma</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>SK Rapid Wien</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>FC Santa Coloma</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>0x568429d159b17f3e17f83384554dcb4508d96942d411a493bfcdd9af2fd2df07</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>L19558557</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>1785100795</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>1785349800</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>51.773196</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>0xb86a834aa70af447f0675d386c1849b1c99fbb8415a4a0f57dedbfc3374369c8</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>10.74</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1.2875</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>KF Drita vs Floriana</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>KF Drita</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Floriana</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>0x74cee3640eed67802d8602418d415d7e5f881528425b4aded0a73b883c57f7c2</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>L19556829</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>1785068425</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>1785261600</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>37.356522</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>0x8004902c8df50fb0691955c2dde204aa37aea6ffc9f11cb60795a2b8862e7e34</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1.3188</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>KF Drita -1.5</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>KF Drita vs Floriana</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>KF Drita</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Floriana</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>L19556829</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>1785065693</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>1785261600</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>5.301961</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>0x9d52e065d77a1e2ffa07fa7250522f55f6a20661ddb8ab22b3656a5e5f518751</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2.87</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1.3188</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>KF Drita -1.5</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>KF Drita vs Floriana</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>KF Drita</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Floriana</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>L19556829</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>1785065679</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>1785261600</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>9.003922</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>0xf072d053c048f056d7fa49c75da51e0772df0db003eaf3ddf341cb2fcc16c416</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1.3188</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>KF Drita -1.5</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>KF Drita vs Floriana</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>KF Drita</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Floriana</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>L19556829</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>1785065519</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>1785261600</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>14.117647</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>0xe1a18ecff833fc919588fdf2e22421fae16e5d31600f43cd14887e49499b233e</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>3.01</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1.3325</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>KF Drita -1.5</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>KF Drita vs Floriana</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>KF Drita</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Floriana</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>L19556829</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>1785065131</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>1785261600</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>9.052632</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>0x97e956b7b7cfe7d56ae2e8711191f397ae89244a032e763798c4b0021c72d481</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>3.81</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1.3325</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>KF Drita -1.5</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>KF Drita vs Floriana</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>KF Drita</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Floriana</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>L19556829</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>1785065030</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>1785261600</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>11.458647</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>0x1b6d50b0b2f30b843c8afcdf1bdd77c807787389b518c0d0118f66c5c53154d1</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>1.3325</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>KF Drita -1.5</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>KF Drita vs Floriana</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>KF Drita</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Floriana</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>L19556829</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>1785064974</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>1785261600</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>3.007519</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>0x7de08a0243073e49c6e479dead7f166232ecd3480830513fb8953abf4d30f575</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Vardar</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
           <t>Riga FC vs Vardar</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>Riga FC</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>Vardar</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>0x3df545e9e324274c452d3611c5ff53dc80c8487fce47da81056d17c1b4257d63</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>L19548393</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>1785064838</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>1785258000</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>13.333333</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>0x98d07c005cea52102549964e374db87ed764bdb1840c7e4d0822a34701829208</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>11.17999</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>1.5012</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Riga FC vs Vardar</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Riga FC</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Vardar</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>0x3ce984b8d5a4fd077770e33c33bd5244077e868cb901d0b9544238e72630158d</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>L19548393</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>1785064821</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>1785258000</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>22.304219</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>0x90084d34df7f1c1dba6533a65ec3b370264b980f4ee2f405409784667aef3385</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>13.33</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>KF Drita -1.5</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>KF Drita vs Floriana</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>KF Drita</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Floriana</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>L19556829</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>1785064821</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>1785261600</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>39.205882</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>0xd382b16331a33a8ef623d9f672b5567e3faaf5a8c56a6b1abbd17c5b3bf2447a</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Vardar</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Riga FC vs Vardar</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Riga FC</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Vardar</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>0x3df545e9e324274c452d3611c5ff53dc80c8487fce47da81056d17c1b4257d63</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>L19548393</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>1785064819</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>1785258000</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>13.888889</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>0xc5ab66578686247686091622e73b8f1713617d5de6c2687bbf706bdd9a1c79eb</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>0x594542a29FFceEAeaDD2e67955437c928B51B758</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>4.12</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1.2637</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Riga FC vs Vardar</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Riga FC</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Vardar</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
         <is>
           <t>0x8f444d513fee4c89c59a5fac9732f2bdbc34c255f1e145e912b5e8d3864de79a</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>L19548393</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>1785064813</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>1785258000</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>15.620853</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>0x60648f843dfab3db80e7b11dc76bd422fb1242bf53219948830cbe4d1b29ee2e</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Vardar</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Riga FC vs Vardar</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Riga FC</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Vardar</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>0x3df545e9e324274c452d3611c5ff53dc80c8487fce47da81056d17c1b4257d63</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>L19548393</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1785064792</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>1785258000</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>15.444444</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>0xd4092c9aa9c679f18a84f2d088ee1a8595762c53fd62d16b214a853eff1fde81</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>0x594542a29FFceEAeaDD2e67955437c928B51B758</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>3.67</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1.2637</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Riga FC vs Vardar</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Riga FC</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Vardar</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>0x8f444d513fee4c89c59a5fac9732f2bdbc34c255f1e145e912b5e8d3864de79a</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>L19548393</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1785064770</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>1785258000</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>13.914692</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>0x3a9ab01f5b98d3619f0b7d9da475c1eabc0e13099a65941bdca6bd024e7991b6</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1.2637</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Riga FC vs Vardar</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Riga FC</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Vardar</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>0x8f444d513fee4c89c59a5fac9732f2bdbc34c255f1e145e912b5e8d3864de79a</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>L19548393</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
         <is>
           <t>1785064754</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="S43" t="inlineStr">
         <is>
           <t>1785258000</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="T43" t="inlineStr">
         <is>
           <t>5.118483</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="U43" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="V43" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/UEFA Conference League/trades.xlsx
+++ b/data/sxbet/ligas/UEFA Conference League/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V43"/>
+  <dimension ref="A1:V44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xc2aab73ddffd7075b0f7b62fe496b81e8ff26c527fc6f8f306a4e978d3ed1efd</t>
+          <t>0xe56a8509a245b02e123202b549bc14f2ca45ffdc40b5a7f4cd2c3c0747fde670</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x155C76202e45BE70c50bfeD7eAeA3B98e7716Ff7</t>
+          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,22 +546,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.99999</t>
+          <t>452.16992</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.7437</t>
+          <t>1.905</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>UEFA Conference League</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Riga FC</t>
+          <t>Zira FK</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -571,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Riga FC vs Vardar</t>
+          <t>Zira FK vs Paide Linnameeskond</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Riga FC</t>
+          <t>Zira FK</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Paide Linnameeskond</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x8f444d513fee4c89c59a5fac9732f2bdbc34c255f1e145e912b5e8d3864de79a</t>
+          <t>0x56f6e71f9b6763e5ad84422820347dada907b51c1f11b22e4f4bca1e48f684c7</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19548393</t>
+          <t>L19568228</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785188484</t>
+          <t>1785196074</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785258000</t>
+          <t>1785427200</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2.689062</t>
+          <t>499.635271</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,12 +643,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x145c09d9142ba2cbced4c8388017e78e14aa9401ee12d36d8129500f13df032e</t>
+          <t>0xc2aab73ddffd7075b0f7b62fe496b81e8ff26c527fc6f8f306a4e978d3ed1efd</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x155C76202e45BE70c50bfeD7eAeA3B98e7716Ff7</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -658,22 +658,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>54.69828</t>
+          <t>1.99999</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.5288</t>
+          <t>1.7437</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>KF Drita -1</t>
+          <t>Riga FC</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -683,27 +683,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>KF Drita vs Floriana</t>
+          <t>Riga FC vs Vardar</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>KF Drita</t>
+          <t>Riga FC</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Floriana</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x5412f1c6d1dfb833bab11103f4cc8d7e6df53302c4951b2ac6b6bec4e6f5ef02</t>
+          <t>0x8f444d513fee4c89c59a5fac9732f2bdbc34c255f1e145e912b5e8d3864de79a</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19556829</t>
+          <t>L19548393</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -728,17 +728,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785188240</t>
+          <t>1785188484</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785261600</t>
+          <t>1785258000</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>103.448284</t>
+          <t>2.689062</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,7 +755,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x9cf4023491039f5bb7dac0df23c846094dd01f9dbee02e57798e16c37d85f644</t>
+          <t>0x145c09d9142ba2cbced4c8388017e78e14aa9401ee12d36d8129500f13df032e</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -770,22 +770,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>54.69828</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.395</t>
+          <t>1.5288</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>KF Drita -1</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -795,27 +795,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Riga FC vs Vardar</t>
+          <t>KF Drita vs Floriana</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Riga FC</t>
+          <t>KF Drita</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Floriana</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x4b27547b8aa1ca6be4f6c92d7d7529a6f2db813e76b6e813d964bae73b66325b</t>
+          <t>0x5412f1c6d1dfb833bab11103f4cc8d7e6df53302c4951b2ac6b6bec4e6f5ef02</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19548393</t>
+          <t>L19556829</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -840,17 +840,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785187553</t>
+          <t>1785188240</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785258000</t>
+          <t>1785261600</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>6.708861</t>
+          <t>103.448284</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -867,12 +867,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xc7e6d7d15508ccc8392a870d6681e7b64fd2e6038be310a8a884315b6a1c961c</t>
+          <t>0x9cf4023491039f5bb7dac0df23c846094dd01f9dbee02e57798e16c37d85f644</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x1b1185C2A2d1Ec3CA592f5c21f52dD4aD449163f</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -882,22 +882,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.175</t>
+          <t>1.395</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x493fb5a9e01ebf84f758d2393d26a55e30244a3f9d8b15eb25d6f79450841850</t>
+          <t>0x4b27547b8aa1ca6be4f6c92d7d7529a6f2db813e76b6e813d964bae73b66325b</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785186255</t>
+          <t>1785187553</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>142.857143</t>
+          <t>6.708861</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -979,7 +979,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x97bc06ccc193bcef116dbd3167a750fb9715b73503439c03d33582d95f59a027</t>
+          <t>0xc7e6d7d15508ccc8392a870d6681e7b64fd2e6038be310a8a884315b6a1c961c</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.1125</t>
+          <t>1.175</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>FC Dila Gori</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1019,27 +1019,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Apollon Limassol FC vs FC Dila Gori</t>
+          <t>Riga FC vs Vardar</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Apollon Limassol FC</t>
+          <t>Riga FC</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>FC Dila Gori</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x66b17a5927b2a92224c605c32e8306f8dc8fabb6ccff81abfc5fbafb709f9a22</t>
+          <t>0x493fb5a9e01ebf84f758d2393d26a55e30244a3f9d8b15eb25d6f79450841850</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19548403</t>
+          <t>L19548393</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785186085</t>
+          <t>1785186255</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>222.222222</t>
+          <t>142.857143</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1091,23 +1091,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xa1b38b181df840d94fccfceb9be5cfd1c9808b3603eb40e8e856fea5c36c33f0</t>
+          <t>0x97bc06ccc193bcef116dbd3167a750fb9715b73503439c03d33582d95f59a027</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>0x1b1185C2A2d1Ec3CA592f5c21f52dD4aD449163f</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.1125</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1115,7 +1119,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>FC Dila Gori</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -1123,27 +1131,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>GKS Katowice vs MSK Zilina</t>
+          <t>Apollon Limassol FC vs FC Dila Gori</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Apollon Limassol FC</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>MSK Zilina</t>
+          <t>FC Dila Gori</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x17ea810aed80a43d53397b03233a18bc09fd2fccf8db1130f11e12f7f95c91e7</t>
+          <t>0x66b17a5927b2a92224c605c32e8306f8dc8fabb6ccff81abfc5fbafb709f9a22</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19568244</t>
+          <t>L19548403</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1168,17 +1176,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785184086</t>
+          <t>1785186085</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785258000</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>222.222222</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1195,39 +1203,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xe5723419c39bca85b784eb615a725a9a26a5c239d525f82b27535463ba9d9f88</t>
+          <t>0xa1b38b181df840d94fccfceb9be5cfd1c9808b3603eb40e8e856fea5c36c33f0</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>203.62057</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.8838</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UEFA Conference League</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Panathinaikos</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -1235,27 +1235,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Panathinaikos vs Paksi SE</t>
+          <t>GKS Katowice vs MSK Zilina</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>MSK Zilina</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x9747c98c82c1e1aeebd441f71649b575a324218f5bb412402cb90fb1639eb40f</t>
+          <t>0x17ea810aed80a43d53397b03233a18bc09fd2fccf8db1130f11e12f7f95c91e7</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19568307</t>
+          <t>L19568244</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785178979</t>
+          <t>1785184086</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>230.405171</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1307,7 +1307,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x9d2c4725405077ca1bceaff142e2ed3d4e9ff5d3b138a2f49b31afb87c9fa625</t>
+          <t>0xe5723419c39bca85b784eb615a725a9a26a5c239d525f82b27535463ba9d9f88</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1315,15 +1315,19 @@
           <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>25.92059</t>
+          <t>203.62057</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.1125</t>
+          <t>1.8838</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1331,7 +1335,11 @@
           <t>UEFA Conference League</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Panathinaikos</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -1394,7 +1402,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>230.405244</t>
+          <t>230.405171</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1411,27 +1419,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x09e55e9944cfa459297c6a9f1bd507159b106de1f3987c8394a2b0fd67f3ba3b</t>
+          <t>0x9d2c4725405077ca1bceaff142e2ed3d4e9ff5d3b138a2f49b31afb87c9fa625</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>82.92</t>
+          <t>25.92059</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.1125</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1439,11 +1443,7 @@
           <t>UEFA Conference League</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>FC CSKA Sofia 1948</t>
-        </is>
-      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -1451,27 +1451,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>FC CSKA Sofia 1948 vs FC Spartak Trnava</t>
+          <t>Panathinaikos vs Paksi SE</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>FC CSKA Sofia 1948</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>FC Spartak Trnava</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x0f0e918dc732446e9ce6f03b0a5b34d1a075bcff9ed3e2ca33563b8eea52d345</t>
+          <t>0x9747c98c82c1e1aeebd441f71649b575a324218f5bb412402cb90fb1639eb40f</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19548391</t>
+          <t>L19568307</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785178520</t>
+          <t>1785178979</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1785259800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>123.761194</t>
+          <t>230.405244</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1523,7 +1523,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xff24d53e0d12e00d437b591e035e6a102c9ec294448637ea1d827288ccdfd669</t>
+          <t>0x09e55e9944cfa459297c6a9f1bd507159b106de1f3987c8394a2b0fd67f3ba3b</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1538,12 +1538,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>32.29</t>
+          <t>82.92</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.7025</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785178483</t>
+          <t>1785178520</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>45.964413</t>
+          <t>123.761194</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1635,7 +1635,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xa2145f7f39e67fd641cdc795fb35638f93441f575672f474dcbb129d212b2071</t>
+          <t>0xff24d53e0d12e00d437b591e035e6a102c9ec294448637ea1d827288ccdfd669</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1643,23 +1643,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>282.04998</t>
+          <t>32.29</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.8675</t>
+          <t>1.7025</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>FC CSKA Sofia 1948</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -1667,27 +1675,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>KF Drita vs Floriana</t>
+          <t>FC CSKA Sofia 1948 vs FC Spartak Trnava</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>KF Drita</t>
+          <t>FC CSKA Sofia 1948</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Floriana</t>
+          <t>FC Spartak Trnava</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xd67d116960d6336d573e0df6e68fbc4925de62b55e56c443ceca3b50f83a0f30</t>
+          <t>0x0f0e918dc732446e9ce6f03b0a5b34d1a075bcff9ed3e2ca33563b8eea52d345</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19556829</t>
+          <t>L19548391</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1712,17 +1720,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785178247</t>
+          <t>1785178483</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1785261600</t>
+          <t>1785259800</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>325.12966</t>
+          <t>45.964413</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1739,7 +1747,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x81f3111a3468acf1de52d30ac0604c9ee06fc1a0787546268f23addd010feff2</t>
+          <t>0xa2145f7f39e67fd641cdc795fb35638f93441f575672f474dcbb129d212b2071</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1747,46 +1755,38 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>101.96</t>
+          <t>282.04998</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.8013</t>
+          <t>1.8675</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>UEFA Conference League</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>KF Drita vs Floriana</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>KF Drita</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>UEFA Conference League</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>KF Drita vs Floriana</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>KF Drita</t>
-        </is>
-      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>Floriana</t>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x09c0b1c15b6ea28d2c0107f466fade6e9caf4c75d4f55998d43c1e51232e5234</t>
+          <t>0xd67d116960d6336d573e0df6e68fbc4925de62b55e56c443ceca3b50f83a0f30</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785175205</t>
+          <t>1785178247</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>127.25117</t>
+          <t>325.12966</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1851,12 +1851,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xe051c5dca29cf389a307215b76298a2e45bf4baccb56422aafc9a3c300c155dd</t>
+          <t>0x81f3111a3468acf1de52d30ac0604c9ee06fc1a0787546268f23addd010feff2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>18.61997</t>
+          <t>101.96</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785174328</t>
+          <t>1785175205</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>23.238652</t>
+          <t>127.25117</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1963,7 +1963,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xdaaf4df1704b396668995377988eea9bc6831ef12573030f333c949030199143</t>
+          <t>0xe051c5dca29cf389a307215b76298a2e45bf4baccb56422aafc9a3c300c155dd</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>21.48999</t>
+          <t>18.61997</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785174135</t>
+          <t>1785174328</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>26.82058</t>
+          <t>23.238652</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2075,31 +2075,39 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x94f8a12cc97509762210745df2b56516620b6491bd6d10909e3496335a55dd21</t>
+          <t>0xdaaf4df1704b396668995377988eea9bc6831ef12573030f333c949030199143</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x960070fC76573ff9c086dB473f99CA99ea914dd6</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>21.48999</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.6225</t>
+          <t>1.8013</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>KF Drita</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -2122,7 +2130,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
+          <t>0x09c0b1c15b6ea28d2c0107f466fade6e9caf4c75d4f55998d43c1e51232e5234</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2152,7 +2160,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785172928</t>
+          <t>1785174135</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2162,7 +2170,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>20.883534</t>
+          <t>26.82058</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2179,54 +2187,46 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x0f77d19b1a11d1f8146d9103f3be3cbc4c3ff95c3bafe707daeb72cd0f7580ae</t>
+          <t>0x94f8a12cc97509762210745df2b56516620b6491bd6d10909e3496335a55dd21</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x960070fC76573ff9c086dB473f99CA99ea914dd6</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>16.67997</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.815</t>
+          <t>1.6225</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>UEFA Conference League</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>KF Drita vs Floriana</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
         <is>
           <t>KF Drita</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>UEFA Conference League</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>KF Drita vs Floriana</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>KF Drita</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>Floriana</t>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x09c0b1c15b6ea28d2c0107f466fade6e9caf4c75d4f55998d43c1e51232e5234</t>
+          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785172335</t>
+          <t>1785172928</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>20.466221</t>
+          <t>20.883534</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2291,31 +2291,39 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x5e2fb7a1e61868dc87b64881470b8319cd876087d156626150e830a7cf27d189</t>
+          <t>0x0f77d19b1a11d1f8146d9103f3be3cbc4c3ff95c3bafe707daeb72cd0f7580ae</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>16.67997</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.285</t>
+          <t>1.815</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KF Drita</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -2323,27 +2331,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Apollon Limassol FC vs FC Dila Gori</t>
+          <t>KF Drita vs Floriana</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Apollon Limassol FC</t>
+          <t>KF Drita</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>FC Dila Gori</t>
+          <t>Floriana</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x000702f32390bc2acb841097855bbcf831db778647d8ef65ce0eb22695863bdc</t>
+          <t>0x09c0b1c15b6ea28d2c0107f466fade6e9caf4c75d4f55998d43c1e51232e5234</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19548403</t>
+          <t>L19556829</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2368,17 +2376,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785171495</t>
+          <t>1785172335</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1785258000</t>
+          <t>1785261600</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>294.035088</t>
+          <t>20.466221</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2395,27 +2403,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x00ae6c3a5ed7e25ed4adcc5d726b723762a6ddfb651274951dc984b567621eef</t>
+          <t>0x5e2fb7a1e61868dc87b64881470b8319cd876087d156626150e830a7cf27d189</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.1675</t>
+          <t>1.285</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2423,11 +2427,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Dukagjini</t>
-        </is>
-      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -2435,27 +2435,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Dukagjini vs FC Lugano</t>
+          <t>Apollon Limassol FC vs FC Dila Gori</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Dukagjini</t>
+          <t>Apollon Limassol FC</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>FC Lugano</t>
+          <t>FC Dila Gori</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xb4e6b34f8bd841e610d92a6e94ae60f508da52a98987521a70ab1ff92547c4a1</t>
+          <t>0x000702f32390bc2acb841097855bbcf831db778647d8ef65ce0eb22695863bdc</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19578699</t>
+          <t>L19548403</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2480,17 +2480,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785164985</t>
+          <t>1785171495</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1785335400</t>
+          <t>1785258000</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>10.859701</t>
+          <t>294.035088</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2507,7 +2507,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x3d30d13f4f7532b8458d9fcb5fefaa11b7fdc084e05b8ea5921efdd1815c2b2e</t>
+          <t>0x00ae6c3a5ed7e25ed4adcc5d726b723762a6ddfb651274951dc984b567621eef</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.802</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785162974</t>
+          <t>1785164985</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>10.758209</t>
+          <t>10.859701</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2619,23 +2619,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x79647a96f9215372245b4b53f196e63141ae86a1ea37ec3c520054924f339f07</t>
+          <t>0x3d30d13f4f7532b8458d9fcb5fefaa11b7fdc084e05b8ea5921efdd1815c2b2e</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>1.802</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.2975</t>
+          <t>1.1675</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2643,7 +2647,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dukagjini</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -2651,27 +2659,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Apollon Limassol FC vs FC Dila Gori</t>
+          <t>Dukagjini vs FC Lugano</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Apollon Limassol FC</t>
+          <t>Dukagjini</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>FC Dila Gori</t>
+          <t>FC Lugano</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x000702f32390bc2acb841097855bbcf831db778647d8ef65ce0eb22695863bdc</t>
+          <t>0xb4e6b34f8bd841e610d92a6e94ae60f508da52a98987521a70ab1ff92547c4a1</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19548403</t>
+          <t>L19578699</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2696,17 +2704,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785160034</t>
+          <t>1785162974</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1785258000</t>
+          <t>1785335400</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>24.470588</t>
+          <t>10.758209</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2723,54 +2731,46 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xc738fb5ab6b1a30b7c6c1ec2cd7f70095001f6e7c404f7f168998f3ce0923565</t>
+          <t>0x79647a96f9215372245b4b53f196e63141ae86a1ea37ec3c520054924f339f07</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>281.53996</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.8588</t>
+          <t>1.2975</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>UEFA Conference League</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Apollon Limassol FC vs FC Dila Gori</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>Apollon Limassol FC</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>UEFA Conference League</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Apollon Limassol FC vs FC Dila Gori</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Apollon Limassol FC</t>
-        </is>
-      </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>FC Dila Gori</t>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x6b053f472a4306388af8fe5ea15275295a0aae1b19a9f51e5b3c924cb4aacd4d</t>
+          <t>0x000702f32390bc2acb841097855bbcf831db778647d8ef65ce0eb22695863bdc</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785159837</t>
+          <t>1785160034</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>327.848571</t>
+          <t>24.470588</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2835,12 +2835,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x0b99d0d305609060f8495bfe5f8c95e1a0b399ad11cc9adf4f34153f68c97d71</t>
+          <t>0xc738fb5ab6b1a30b7c6c1ec2cd7f70095001f6e7c404f7f168998f3ce0923565</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2850,47 +2850,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>281.53996</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.1025</t>
+          <t>1.8588</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>UEFA Conference League</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
+          <t>Apollon Limassol FC</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Apollon Limassol FC vs FC Dila Gori</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Apollon Limassol FC</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t>FC Dila Gori</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>UEFA Conference League</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Apollon Limassol FC vs FC Dila Gori</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Apollon Limassol FC</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>FC Dila Gori</t>
-        </is>
-      </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x66b17a5927b2a92224c605c32e8306f8dc8fabb6ccff81abfc5fbafb709f9a22</t>
+          <t>0x6b053f472a4306388af8fe5ea15275295a0aae1b19a9f51e5b3c924cb4aacd4d</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785143243</t>
+          <t>1785159837</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>9.853659</t>
+          <t>327.848571</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2947,12 +2947,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xa2274ee0f4684479f0988ac6a5139708014cf026476c7cf9b37b3a416e7b5747</t>
+          <t>0x0b99d0d305609060f8495bfe5f8c95e1a0b399ad11cc9adf4f34153f68c97d71</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x1b1185C2A2d1Ec3CA592f5c21f52dD4aD449163f</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.0625</t>
+          <t>1.1025</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Paide Linnameeskond</t>
+          <t>FC Dila Gori</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2987,27 +2987,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Zira FK vs Paide Linnameeskond</t>
+          <t>Apollon Limassol FC vs FC Dila Gori</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Zira FK</t>
+          <t>Apollon Limassol FC</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Paide Linnameeskond</t>
+          <t>FC Dila Gori</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0xc2274f3d5306fe3b7bf272b7cfce16894bf01595fd8fa3181858809c5afd887d</t>
+          <t>0x66b17a5927b2a92224c605c32e8306f8dc8fabb6ccff81abfc5fbafb709f9a22</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19568228</t>
+          <t>L19548403</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3032,17 +3032,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785123628</t>
+          <t>1785143243</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1785427200</t>
+          <t>1785258000</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>9.853659</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3059,12 +3059,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x4b249266f4a129a90a4f4289f80efd22864a0b55a615a30c01a744c9e6fa007e</t>
+          <t>0xa2274ee0f4684479f0988ac6a5139708014cf026476c7cf9b37b3a416e7b5747</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x1b1185C2A2d1Ec3CA592f5c21f52dD4aD449163f</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.2463</t>
+          <t>1.0625</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>FC Spartak Trnava</t>
+          <t>Paide Linnameeskond</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3099,27 +3099,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>FC CSKA Sofia 1948 vs FC Spartak Trnava</t>
+          <t>Zira FK vs Paide Linnameeskond</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>FC CSKA Sofia 1948</t>
+          <t>Zira FK</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>FC Spartak Trnava</t>
+          <t>Paide Linnameeskond</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0xe6d3ed6a25306fb2793f56682ed261dbde83f239772758b37aeecc6a973830a6</t>
+          <t>0xc2274f3d5306fe3b7bf272b7cfce16894bf01595fd8fa3181858809c5afd887d</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19548391</t>
+          <t>L19568228</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3144,17 +3144,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785114331</t>
+          <t>1785123628</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1785259800</t>
+          <t>1785427200</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>20.020305</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3171,23 +3171,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xbcaacd1e8dc7d60abd70f28c7ffba7450e4c76519b53d45633047b2e308ce8df</t>
+          <t>0x4b249266f4a129a90a4f4289f80efd22864a0b55a615a30c01a744c9e6fa007e</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.835</t>
+          <t>1.2463</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3195,7 +3199,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>FC Spartak Trnava</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -3203,27 +3211,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Dukagjini vs FC Lugano</t>
+          <t>FC CSKA Sofia 1948 vs FC Spartak Trnava</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Dukagjini</t>
+          <t>FC CSKA Sofia 1948</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>FC Lugano</t>
+          <t>FC Spartak Trnava</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0xb4e6b34f8bd841e610d92a6e94ae60f508da52a98987521a70ab1ff92547c4a1</t>
+          <t>0xe6d3ed6a25306fb2793f56682ed261dbde83f239772758b37aeecc6a973830a6</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19578699</t>
+          <t>L19548391</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3248,17 +3256,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785108140</t>
+          <t>1785114331</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1785335400</t>
+          <t>1785259800</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>5.02994</t>
+          <t>20.020305</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3275,23 +3283,23 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0xc4f834cac0960a0d1d3dfd961f4ed03d26a908325b0613bbc25d8271e7ea9596</t>
+          <t>0xbcaacd1e8dc7d60abd70f28c7ffba7450e4c76519b53d45633047b2e308ce8df</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.4062</t>
+          <t>1.835</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3307,27 +3315,27 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>KF Drita vs Floriana</t>
+          <t>Dukagjini vs FC Lugano</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>KF Drita</t>
+          <t>Dukagjini</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Floriana</t>
+          <t>FC Lugano</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0xd80db7f29b1a9bf7479fe759db5892459ba76d2573c8028c682ca72ca26fa563</t>
+          <t>0xb4e6b34f8bd841e610d92a6e94ae60f508da52a98987521a70ab1ff92547c4a1</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>L19556829</t>
+          <t>L19578699</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3352,17 +3360,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785102921</t>
+          <t>1785108140</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>1785261600</t>
+          <t>1785335400</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>5.02994</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3379,7 +3387,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x642cead4cce6abf15e60b5f101292963653928af192a53d61cf13be1f5735346</t>
+          <t>0xc4f834cac0960a0d1d3dfd961f4ed03d26a908325b0613bbc25d8271e7ea9596</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3387,31 +3395,23 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>25.11</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.4062</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>SK Rapid Wien -2.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -3419,27 +3419,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>SK Rapid Wien vs FC Santa Coloma</t>
+          <t>KF Drita vs Floriana</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>SK Rapid Wien</t>
+          <t>KF Drita</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>FC Santa Coloma</t>
+          <t>Floriana</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x568429d159b17f3e17f83384554dcb4508d96942d411a493bfcdd9af2fd2df07</t>
+          <t>0xd80db7f29b1a9bf7479fe759db5892459ba76d2573c8028c682ca72ca26fa563</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>L19558557</t>
+          <t>L19556829</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3464,17 +3464,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785100795</t>
+          <t>1785102921</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>1785349800</t>
+          <t>1785261600</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>51.773196</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3491,7 +3491,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0xb86a834aa70af447f0675d386c1849b1c99fbb8415a4a0f57dedbfc3374369c8</t>
+          <t>0x642cead4cce6abf15e60b5f101292963653928af192a53d61cf13be1f5735346</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3499,23 +3499,31 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>10.74</t>
+          <t>25.11</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.2875</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>UEFA Conference League</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>SK Rapid Wien -2.5</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -3523,27 +3531,27 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>KF Drita vs Floriana</t>
+          <t>SK Rapid Wien vs FC Santa Coloma</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>KF Drita</t>
+          <t>SK Rapid Wien</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Floriana</t>
+          <t>FC Santa Coloma</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x74cee3640eed67802d8602418d415d7e5f881528425b4aded0a73b883c57f7c2</t>
+          <t>0x568429d159b17f3e17f83384554dcb4508d96942d411a493bfcdd9af2fd2df07</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19556829</t>
+          <t>L19558557</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3568,17 +3576,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785068425</t>
+          <t>1785100795</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1785261600</t>
+          <t>1785349800</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>37.356522</t>
+          <t>51.773196</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3595,39 +3603,31 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x8004902c8df50fb0691955c2dde204aa37aea6ffc9f11cb60795a2b8862e7e34</t>
+          <t>0xb86a834aa70af447f0675d386c1849b1c99fbb8415a4a0f57dedbfc3374369c8</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>10.74</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.3188</t>
+          <t>1.2875</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>KF Drita -1.5</t>
-        </is>
-      </c>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
+          <t>0x74cee3640eed67802d8602418d415d7e5f881528425b4aded0a73b883c57f7c2</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785065693</t>
+          <t>1785068425</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>5.301961</t>
+          <t>37.356522</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3707,7 +3707,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x9d52e065d77a1e2ffa07fa7250522f55f6a20661ddb8ab22b3656a5e5f518751</t>
+          <t>0x8004902c8df50fb0691955c2dde204aa37aea6ffc9f11cb60795a2b8862e7e34</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3722,7 +3722,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785065679</t>
+          <t>1785065693</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>9.003922</t>
+          <t>5.301961</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3819,7 +3819,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0xf072d053c048f056d7fa49c75da51e0772df0db003eaf3ddf341cb2fcc16c416</t>
+          <t>0x9d52e065d77a1e2ffa07fa7250522f55f6a20661ddb8ab22b3656a5e5f518751</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785065519</t>
+          <t>1785065679</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3914,7 +3914,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>14.117647</t>
+          <t>9.003922</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3931,7 +3931,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0xe1a18ecff833fc919588fdf2e22421fae16e5d31600f43cd14887e49499b233e</t>
+          <t>0xf072d053c048f056d7fa49c75da51e0772df0db003eaf3ddf341cb2fcc16c416</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.3325</t>
+          <t>1.3188</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785065131</t>
+          <t>1785065519</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>9.052632</t>
+          <t>14.117647</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4043,7 +4043,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x97e956b7b7cfe7d56ae2e8711191f397ae89244a032e763798c4b0021c72d481</t>
+          <t>0xe1a18ecff833fc919588fdf2e22421fae16e5d31600f43cd14887e49499b233e</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785065030</t>
+          <t>1785065131</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>11.458647</t>
+          <t>9.052632</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4155,7 +4155,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x1b6d50b0b2f30b843c8afcdf1bdd77c807787389b518c0d0118f66c5c53154d1</t>
+          <t>0x97e956b7b7cfe7d56ae2e8711191f397ae89244a032e763798c4b0021c72d481</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785064974</t>
+          <t>1785065030</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>3.007519</t>
+          <t>11.458647</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4267,7 +4267,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x7de08a0243073e49c6e479dead7f166232ecd3480830513fb8953abf4d30f575</t>
+          <t>0x1b6d50b0b2f30b843c8afcdf1bdd77c807787389b518c0d0118f66c5c53154d1</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4282,22 +4282,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.3325</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>KF Drita -1.5</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4307,27 +4307,27 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Riga FC vs Vardar</t>
+          <t>KF Drita vs Floriana</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Riga FC</t>
+          <t>KF Drita</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Floriana</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0x3df545e9e324274c452d3611c5ff53dc80c8487fce47da81056d17c1b4257d63</t>
+          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>L19548393</t>
+          <t>L19556829</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4352,17 +4352,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785064838</t>
+          <t>1785064974</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>1785258000</t>
+          <t>1785261600</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>13.333333</t>
+          <t>3.007519</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4379,7 +4379,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x98d07c005cea52102549964e374db87ed764bdb1840c7e4d0822a34701829208</t>
+          <t>0x7de08a0243073e49c6e479dead7f166232ecd3480830513fb8953abf4d30f575</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4387,23 +4387,31 @@
           <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>11.17999</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Vardar</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -4426,7 +4434,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x3ce984b8d5a4fd077770e33c33bd5244077e868cb901d0b9544238e72630158d</t>
+          <t>0x3df545e9e324274c452d3611c5ff53dc80c8487fce47da81056d17c1b4257d63</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4456,7 +4464,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785064821</t>
+          <t>1785064838</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4466,7 +4474,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>22.304219</t>
+          <t>13.333333</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4483,7 +4491,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x90084d34df7f1c1dba6533a65ec3b370264b980f4ee2f405409784667aef3385</t>
+          <t>0x98d07c005cea52102549964e374db87ed764bdb1840c7e4d0822a34701829208</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4491,19 +4499,15 @@
           <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>11.17999</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4511,11 +4515,7 @@
           <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>KF Drita -1.5</t>
-        </is>
-      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -4523,27 +4523,27 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>KF Drita vs Floriana</t>
+          <t>Riga FC vs Vardar</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>KF Drita</t>
+          <t>Riga FC</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Floriana</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
+          <t>0x3ce984b8d5a4fd077770e33c33bd5244077e868cb901d0b9544238e72630158d</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>L19556829</t>
+          <t>L19548393</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>1785261600</t>
+          <t>1785258000</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>39.205882</t>
+          <t>22.304219</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4595,7 +4595,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0xd382b16331a33a8ef623d9f672b5567e3faaf5a8c56a6b1abbd17c5b3bf2447a</t>
+          <t>0x90084d34df7f1c1dba6533a65ec3b370264b980f4ee2f405409784667aef3385</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4610,22 +4610,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>KF Drita -1.5</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4635,27 +4635,27 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Riga FC vs Vardar</t>
+          <t>KF Drita vs Floriana</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Riga FC</t>
+          <t>KF Drita</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Floriana</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x3df545e9e324274c452d3611c5ff53dc80c8487fce47da81056d17c1b4257d63</t>
+          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>L19548393</t>
+          <t>L19556829</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4680,17 +4680,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785064819</t>
+          <t>1785064821</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>1785258000</t>
+          <t>1785261600</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>13.888889</t>
+          <t>39.205882</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4707,23 +4707,27 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0xc5ab66578686247686091622e73b8f1713617d5de6c2687bbf706bdd9a1c79eb</t>
+          <t>0xd382b16331a33a8ef623d9f672b5567e3faaf5a8c56a6b1abbd17c5b3bf2447a</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0x594542a29FFceEAeaDD2e67955437c928B51B758</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.2637</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4731,7 +4735,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Vardar</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -4754,7 +4762,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x8f444d513fee4c89c59a5fac9732f2bdbc34c255f1e145e912b5e8d3864de79a</t>
+          <t>0x3df545e9e324274c452d3611c5ff53dc80c8487fce47da81056d17c1b4257d63</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4784,7 +4792,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785064813</t>
+          <t>1785064819</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4794,7 +4802,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>15.620853</t>
+          <t>13.888889</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4811,27 +4819,23 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x60648f843dfab3db80e7b11dc76bd422fb1242bf53219948830cbe4d1b29ee2e</t>
+          <t>0xc5ab66578686247686091622e73b8f1713617d5de6c2687bbf706bdd9a1c79eb</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x594542a29FFceEAeaDD2e67955437c928B51B758</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.2637</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4839,34 +4843,30 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Riga FC vs Vardar</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Riga FC</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
         <is>
           <t>Vardar</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>UEFA Conference League</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Riga FC vs Vardar</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Riga FC</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>Vardar</t>
-        </is>
-      </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x3df545e9e324274c452d3611c5ff53dc80c8487fce47da81056d17c1b4257d63</t>
+          <t>0x8f444d513fee4c89c59a5fac9732f2bdbc34c255f1e145e912b5e8d3864de79a</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785064792</t>
+          <t>1785064813</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>15.444444</t>
+          <t>15.620853</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4923,23 +4923,27 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0xd4092c9aa9c679f18a84f2d088ee1a8595762c53fd62d16b214a853eff1fde81</t>
+          <t>0x60648f843dfab3db80e7b11dc76bd422fb1242bf53219948830cbe4d1b29ee2e</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0x594542a29FFceEAeaDD2e67955437c928B51B758</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.2637</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4947,7 +4951,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Vardar</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -4970,7 +4978,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x8f444d513fee4c89c59a5fac9732f2bdbc34c255f1e145e912b5e8d3864de79a</t>
+          <t>0x3df545e9e324274c452d3611c5ff53dc80c8487fce47da81056d17c1b4257d63</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -5000,7 +5008,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1785064770</t>
+          <t>1785064792</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -5010,7 +5018,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>13.914692</t>
+          <t>15.444444</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -5027,18 +5035,18 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x3a9ab01f5b98d3619f0b7d9da475c1eabc0e13099a65941bdca6bd024e7991b6</t>
+          <t>0xd4092c9aa9c679f18a84f2d088ee1a8595762c53fd62d16b214a853eff1fde81</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+          <t>0x594542a29FFceEAeaDD2e67955437c928B51B758</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -5104,25 +5112,129 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
+          <t>1785064770</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>1785258000</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>13.914692</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>0x3a9ab01f5b98d3619f0b7d9da475c1eabc0e13099a65941bdca6bd024e7991b6</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1.2637</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Riga FC vs Vardar</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Riga FC</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Vardar</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>0x8f444d513fee4c89c59a5fac9732f2bdbc34c255f1e145e912b5e8d3864de79a</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>L19548393</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
           <t>1785064754</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>1785258000</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>5.118483</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="U44" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr">
+      <c r="V44" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/UEFA Conference League/trades.xlsx
+++ b/data/sxbet/ligas/UEFA Conference League/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V44"/>
+  <dimension ref="A1:V48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xe56a8509a245b02e123202b549bc14f2ca45ffdc40b5a7f4cd2c3c0747fde670</t>
+          <t>0x3986ccac9da8fd1e2ec5eb9738ca6572eaf2aeb0920147dc7d704cdc2332d387</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,22 +546,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>452.16992</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.905</t>
+          <t>1.2888</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>UEFA Conference League</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Zira FK</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -571,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Zira FK vs Paide Linnameeskond</t>
+          <t>Dukagjini vs FC Lugano</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Zira FK</t>
+          <t>Dukagjini</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Paide Linnameeskond</t>
+          <t>FC Lugano</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x56f6e71f9b6763e5ad84422820347dada907b51c1f11b22e4f4bca1e48f684c7</t>
+          <t>0x1f60001b19ddfc41630c6822a3d47aa8cf8680cef1620d6262024bae4641609b</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19568228</t>
+          <t>L19578699</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785196074</t>
+          <t>1785203409</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785427200</t>
+          <t>1785335400</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>499.635271</t>
+          <t>8.207792</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,12 +643,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xc2aab73ddffd7075b0f7b62fe496b81e8ff26c527fc6f8f306a4e978d3ed1efd</t>
+          <t>0x6370d092d3abe8f1798c07306e22480e361fa8550787500075f06ff338a8ebd6</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x155C76202e45BE70c50bfeD7eAeA3B98e7716Ff7</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -658,17 +658,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.99999</t>
+          <t>156.44</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.7437</t>
+          <t>1.865</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>UEFA Conference League</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x8f444d513fee4c89c59a5fac9732f2bdbc34c255f1e145e912b5e8d3864de79a</t>
+          <t>0xafe00bc468bca0fb7885d652a99b556a6d04f550216ba1d8550ec2732ba07436</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785188484</t>
+          <t>1785202680</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2.689062</t>
+          <t>180.855491</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,39 +755,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x145c09d9142ba2cbced4c8388017e78e14aa9401ee12d36d8129500f13df032e</t>
+          <t>0x1567a1c54e4cdeaac7c846b9591b4c414d90a932154ea48c45a261cffc97b3aa</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>54.69828</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.5288</t>
+          <t>1.2888</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>KF Drita -1</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -795,27 +787,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>KF Drita vs Floriana</t>
+          <t>SK Rapid Wien vs FC Santa Coloma</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>KF Drita</t>
+          <t>SK Rapid Wien</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Floriana</t>
+          <t>FC Santa Coloma</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x5412f1c6d1dfb833bab11103f4cc8d7e6df53302c4951b2ac6b6bec4e6f5ef02</t>
+          <t>0xcf09c10cb205e31ce255c67c424f013a3469ff7cc8e6cc11a0da2738847a6366</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19556829</t>
+          <t>L19558557</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -840,17 +832,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785188240</t>
+          <t>1785199330</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785261600</t>
+          <t>1785349800</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>103.448284</t>
+          <t>17.316017</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -867,12 +859,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x9cf4023491039f5bb7dac0df23c846094dd01f9dbee02e57798e16c37d85f644</t>
+          <t>0x3e339f206f2088c795c4a0636e7271d6124859ebaa118a7c8a34e5622d9ca895</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -882,22 +874,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>12.23</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.395</t>
+          <t>1.315</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Asian Handicap (-2)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Brann -2</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -907,27 +899,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Riga FC vs Vardar</t>
+          <t>Brann vs Universitatea Cluj</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Riga FC</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x4b27547b8aa1ca6be4f6c92d7d7529a6f2db813e76b6e813d964bae73b66325b</t>
+          <t>0x3014dbda6053f0222459758b857d801d076de578e0e8806b8a4ed056ec2508af</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19548393</t>
+          <t>L19570054</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -952,17 +944,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785187553</t>
+          <t>1785197201</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1785258000</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>6.708861</t>
+          <t>38.825397</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -979,12 +971,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xc7e6d7d15508ccc8392a870d6681e7b64fd2e6038be310a8a884315b6a1c961c</t>
+          <t>0xe56a8509a245b02e123202b549bc14f2ca45ffdc40b5a7f4cd2c3c0747fde670</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x1b1185C2A2d1Ec3CA592f5c21f52dD4aD449163f</t>
+          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -994,22 +986,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>452.16992</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.175</t>
+          <t>1.905</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>UEFA Conference League</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Zira FK</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1019,27 +1011,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Riga FC vs Vardar</t>
+          <t>Zira FK vs Paide Linnameeskond</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Riga FC</t>
+          <t>Zira FK</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Paide Linnameeskond</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x493fb5a9e01ebf84f758d2393d26a55e30244a3f9d8b15eb25d6f79450841850</t>
+          <t>0x56f6e71f9b6763e5ad84422820347dada907b51c1f11b22e4f4bca1e48f684c7</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19548393</t>
+          <t>L19568228</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1064,17 +1056,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785186255</t>
+          <t>1785196074</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1785258000</t>
+          <t>1785427200</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>142.857143</t>
+          <t>499.635271</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1091,12 +1083,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x97bc06ccc193bcef116dbd3167a750fb9715b73503439c03d33582d95f59a027</t>
+          <t>0xc2aab73ddffd7075b0f7b62fe496b81e8ff26c527fc6f8f306a4e978d3ed1efd</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x1b1185C2A2d1Ec3CA592f5c21f52dD4aD449163f</t>
+          <t>0x155C76202e45BE70c50bfeD7eAeA3B98e7716Ff7</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1106,12 +1098,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1.99999</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.1125</t>
+          <t>1.7437</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1121,7 +1113,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>FC Dila Gori</t>
+          <t>Riga FC</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1131,27 +1123,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Apollon Limassol FC vs FC Dila Gori</t>
+          <t>Riga FC vs Vardar</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Apollon Limassol FC</t>
+          <t>Riga FC</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>FC Dila Gori</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x66b17a5927b2a92224c605c32e8306f8dc8fabb6ccff81abfc5fbafb709f9a22</t>
+          <t>0x8f444d513fee4c89c59a5fac9732f2bdbc34c255f1e145e912b5e8d3864de79a</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19548403</t>
+          <t>L19548393</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1176,7 +1168,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785186085</t>
+          <t>1785188484</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1186,7 +1178,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>222.222222</t>
+          <t>2.689062</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1203,31 +1195,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xa1b38b181df840d94fccfceb9be5cfd1c9808b3603eb40e8e856fea5c36c33f0</t>
+          <t>0x145c09d9142ba2cbced4c8388017e78e14aa9401ee12d36d8129500f13df032e</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>54.69828</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.5288</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>KF Drita -1</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -1235,27 +1235,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>GKS Katowice vs MSK Zilina</t>
+          <t>KF Drita vs Floriana</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>KF Drita</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>MSK Zilina</t>
+          <t>Floriana</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x17ea810aed80a43d53397b03233a18bc09fd2fccf8db1130f11e12f7f95c91e7</t>
+          <t>0x5412f1c6d1dfb833bab11103f4cc8d7e6df53302c4951b2ac6b6bec4e6f5ef02</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19568244</t>
+          <t>L19556829</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1280,17 +1280,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785184086</t>
+          <t>1785188240</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785261600</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>103.448284</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1307,12 +1307,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xe5723419c39bca85b784eb615a725a9a26a5c239d525f82b27535463ba9d9f88</t>
+          <t>0x9cf4023491039f5bb7dac0df23c846094dd01f9dbee02e57798e16c37d85f644</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1322,22 +1322,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>203.62057</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.8838</t>
+          <t>1.395</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UEFA Conference League</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1347,27 +1347,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Panathinaikos vs Paksi SE</t>
+          <t>Riga FC vs Vardar</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Riga FC</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x9747c98c82c1e1aeebd441f71649b575a324218f5bb412402cb90fb1639eb40f</t>
+          <t>0x4b27547b8aa1ca6be4f6c92d7d7529a6f2db813e76b6e813d964bae73b66325b</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19568307</t>
+          <t>L19548393</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1392,17 +1392,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785178979</t>
+          <t>1785187553</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785258000</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>230.405171</t>
+          <t>6.708861</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1419,31 +1419,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x9d2c4725405077ca1bceaff142e2ed3d4e9ff5d3b138a2f49b31afb87c9fa625</t>
+          <t>0xc7e6d7d15508ccc8392a870d6681e7b64fd2e6038be310a8a884315b6a1c961c</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>0x1b1185C2A2d1Ec3CA592f5c21f52dD4aD449163f</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>25.92059</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.1125</t>
+          <t>1.175</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UEFA Conference League</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -1451,27 +1459,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Panathinaikos vs Paksi SE</t>
+          <t>Riga FC vs Vardar</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Riga FC</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x9747c98c82c1e1aeebd441f71649b575a324218f5bb412402cb90fb1639eb40f</t>
+          <t>0x493fb5a9e01ebf84f758d2393d26a55e30244a3f9d8b15eb25d6f79450841850</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19568307</t>
+          <t>L19548393</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1496,17 +1504,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785178979</t>
+          <t>1785186255</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785258000</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>230.405244</t>
+          <t>142.857143</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1523,12 +1531,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x09e55e9944cfa459297c6a9f1bd507159b106de1f3987c8394a2b0fd67f3ba3b</t>
+          <t>0x97bc06ccc193bcef116dbd3167a750fb9715b73503439c03d33582d95f59a027</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x1b1185C2A2d1Ec3CA592f5c21f52dD4aD449163f</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1538,22 +1546,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>82.92</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.1125</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>UEFA Conference League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>FC CSKA Sofia 1948</t>
+          <t>FC Dila Gori</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1563,27 +1571,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>FC CSKA Sofia 1948 vs FC Spartak Trnava</t>
+          <t>Apollon Limassol FC vs FC Dila Gori</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>FC CSKA Sofia 1948</t>
+          <t>Apollon Limassol FC</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>FC Spartak Trnava</t>
+          <t>FC Dila Gori</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x0f0e918dc732446e9ce6f03b0a5b34d1a075bcff9ed3e2ca33563b8eea52d345</t>
+          <t>0x66b17a5927b2a92224c605c32e8306f8dc8fabb6ccff81abfc5fbafb709f9a22</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19548391</t>
+          <t>L19548403</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1608,17 +1616,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785178520</t>
+          <t>1785186085</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1785259800</t>
+          <t>1785258000</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>123.761194</t>
+          <t>222.222222</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1635,39 +1643,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xff24d53e0d12e00d437b591e035e6a102c9ec294448637ea1d827288ccdfd669</t>
+          <t>0xa1b38b181df840d94fccfceb9be5cfd1c9808b3603eb40e8e856fea5c36c33f0</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>32.29</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.7025</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>UEFA Conference League</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>FC CSKA Sofia 1948</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -1675,27 +1675,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>FC CSKA Sofia 1948 vs FC Spartak Trnava</t>
+          <t>GKS Katowice vs MSK Zilina</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>FC CSKA Sofia 1948</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>FC Spartak Trnava</t>
+          <t>MSK Zilina</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x0f0e918dc732446e9ce6f03b0a5b34d1a075bcff9ed3e2ca33563b8eea52d345</t>
+          <t>0x17ea810aed80a43d53397b03233a18bc09fd2fccf8db1130f11e12f7f95c91e7</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19548391</t>
+          <t>L19568244</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1720,17 +1720,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785178483</t>
+          <t>1785184086</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1785259800</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>45.964413</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1747,31 +1747,39 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xa2145f7f39e67fd641cdc795fb35638f93441f575672f474dcbb129d212b2071</t>
+          <t>0xe5723419c39bca85b784eb615a725a9a26a5c239d525f82b27535463ba9d9f88</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>282.04998</t>
+          <t>203.62057</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.8675</t>
+          <t>1.8838</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Panathinaikos</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -1779,27 +1787,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>KF Drita vs Floriana</t>
+          <t>Panathinaikos vs Paksi SE</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>KF Drita</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Floriana</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xd67d116960d6336d573e0df6e68fbc4925de62b55e56c443ceca3b50f83a0f30</t>
+          <t>0x9747c98c82c1e1aeebd441f71649b575a324218f5bb412402cb90fb1639eb40f</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19556829</t>
+          <t>L19568307</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1824,17 +1832,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785178247</t>
+          <t>1785178979</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1785261600</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>325.12966</t>
+          <t>230.405171</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1851,27 +1859,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x81f3111a3468acf1de52d30ac0604c9ee06fc1a0787546268f23addd010feff2</t>
+          <t>0x9d2c4725405077ca1bceaff142e2ed3d4e9ff5d3b138a2f49b31afb87c9fa625</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>101.96</t>
+          <t>25.92059</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.8013</t>
+          <t>1.1125</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1879,11 +1883,7 @@
           <t>UEFA Conference League</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>KF Drita</t>
-        </is>
-      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -1891,27 +1891,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>KF Drita vs Floriana</t>
+          <t>Panathinaikos vs Paksi SE</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>KF Drita</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Floriana</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x09c0b1c15b6ea28d2c0107f466fade6e9caf4c75d4f55998d43c1e51232e5234</t>
+          <t>0x9747c98c82c1e1aeebd441f71649b575a324218f5bb412402cb90fb1639eb40f</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19556829</t>
+          <t>L19568307</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1936,17 +1936,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785175205</t>
+          <t>1785178979</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1785261600</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>127.25117</t>
+          <t>230.405244</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1963,12 +1963,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xe051c5dca29cf389a307215b76298a2e45bf4baccb56422aafc9a3c300c155dd</t>
+          <t>0x09e55e9944cfa459297c6a9f1bd507159b106de1f3987c8394a2b0fd67f3ba3b</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1978,12 +1978,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>18.61997</t>
+          <t>82.92</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.8013</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>KF Drita</t>
+          <t>FC CSKA Sofia 1948</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2003,27 +2003,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>KF Drita vs Floriana</t>
+          <t>FC CSKA Sofia 1948 vs FC Spartak Trnava</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>KF Drita</t>
+          <t>FC CSKA Sofia 1948</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Floriana</t>
+          <t>FC Spartak Trnava</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x09c0b1c15b6ea28d2c0107f466fade6e9caf4c75d4f55998d43c1e51232e5234</t>
+          <t>0x0f0e918dc732446e9ce6f03b0a5b34d1a075bcff9ed3e2ca33563b8eea52d345</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19556829</t>
+          <t>L19548391</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2048,17 +2048,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785174328</t>
+          <t>1785178520</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1785261600</t>
+          <t>1785259800</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>23.238652</t>
+          <t>123.761194</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2075,12 +2075,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xdaaf4df1704b396668995377988eea9bc6831ef12573030f333c949030199143</t>
+          <t>0xff24d53e0d12e00d437b591e035e6a102c9ec294448637ea1d827288ccdfd669</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2090,12 +2090,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>21.48999</t>
+          <t>32.29</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.8013</t>
+          <t>1.7025</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>KF Drita</t>
+          <t>FC CSKA Sofia 1948</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2115,27 +2115,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>KF Drita vs Floriana</t>
+          <t>FC CSKA Sofia 1948 vs FC Spartak Trnava</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>KF Drita</t>
+          <t>FC CSKA Sofia 1948</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Floriana</t>
+          <t>FC Spartak Trnava</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x09c0b1c15b6ea28d2c0107f466fade6e9caf4c75d4f55998d43c1e51232e5234</t>
+          <t>0x0f0e918dc732446e9ce6f03b0a5b34d1a075bcff9ed3e2ca33563b8eea52d345</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19556829</t>
+          <t>L19548391</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2160,17 +2160,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785174135</t>
+          <t>1785178483</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1785261600</t>
+          <t>1785259800</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>26.82058</t>
+          <t>45.964413</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2187,28 +2187,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x94f8a12cc97509762210745df2b56516620b6491bd6d10909e3496335a55dd21</t>
+          <t>0xa2145f7f39e67fd641cdc795fb35638f93441f575672f474dcbb129d212b2071</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x960070fC76573ff9c086dB473f99CA99ea914dd6</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>282.04998</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.6225</t>
+          <t>1.8675</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
+          <t>0xd67d116960d6336d573e0df6e68fbc4925de62b55e56c443ceca3b50f83a0f30</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785172928</t>
+          <t>1785178247</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>20.883534</t>
+          <t>325.12966</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2291,12 +2291,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x0f77d19b1a11d1f8146d9103f3be3cbc4c3ff95c3bafe707daeb72cd0f7580ae</t>
+          <t>0x81f3111a3468acf1de52d30ac0604c9ee06fc1a0787546268f23addd010feff2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2306,12 +2306,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>16.67997</t>
+          <t>101.96</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.815</t>
+          <t>1.8013</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785172335</t>
+          <t>1785175205</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>20.466221</t>
+          <t>127.25117</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2403,31 +2403,39 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x5e2fb7a1e61868dc87b64881470b8319cd876087d156626150e830a7cf27d189</t>
+          <t>0xe051c5dca29cf389a307215b76298a2e45bf4baccb56422aafc9a3c300c155dd</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>18.61997</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.285</t>
+          <t>1.8013</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>KF Drita</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -2435,27 +2443,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Apollon Limassol FC vs FC Dila Gori</t>
+          <t>KF Drita vs Floriana</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Apollon Limassol FC</t>
+          <t>KF Drita</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>FC Dila Gori</t>
+          <t>Floriana</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x000702f32390bc2acb841097855bbcf831db778647d8ef65ce0eb22695863bdc</t>
+          <t>0x09c0b1c15b6ea28d2c0107f466fade6e9caf4c75d4f55998d43c1e51232e5234</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19548403</t>
+          <t>L19556829</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2480,17 +2488,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785171495</t>
+          <t>1785174328</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1785258000</t>
+          <t>1785261600</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>294.035088</t>
+          <t>23.238652</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2507,12 +2515,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x00ae6c3a5ed7e25ed4adcc5d726b723762a6ddfb651274951dc984b567621eef</t>
+          <t>0xdaaf4df1704b396668995377988eea9bc6831ef12573030f333c949030199143</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2522,22 +2530,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>21.48999</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.1675</t>
+          <t>1.8013</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>UEFA Conference League</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dukagjini</t>
+          <t>KF Drita</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2547,27 +2555,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Dukagjini vs FC Lugano</t>
+          <t>KF Drita vs Floriana</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Dukagjini</t>
+          <t>KF Drita</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>FC Lugano</t>
+          <t>Floriana</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0xb4e6b34f8bd841e610d92a6e94ae60f508da52a98987521a70ab1ff92547c4a1</t>
+          <t>0x09c0b1c15b6ea28d2c0107f466fade6e9caf4c75d4f55998d43c1e51232e5234</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19578699</t>
+          <t>L19556829</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2592,17 +2600,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785164985</t>
+          <t>1785174135</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1785335400</t>
+          <t>1785261600</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>10.859701</t>
+          <t>26.82058</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2619,39 +2627,31 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x3d30d13f4f7532b8458d9fcb5fefaa11b7fdc084e05b8ea5921efdd1815c2b2e</t>
+          <t>0x94f8a12cc97509762210745df2b56516620b6491bd6d10909e3496335a55dd21</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x960070fC76573ff9c086dB473f99CA99ea914dd6</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.802</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.1675</t>
+          <t>1.6225</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Dukagjini</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -2659,27 +2659,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Dukagjini vs FC Lugano</t>
+          <t>KF Drita vs Floriana</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Dukagjini</t>
+          <t>KF Drita</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>FC Lugano</t>
+          <t>Floriana</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0xb4e6b34f8bd841e610d92a6e94ae60f508da52a98987521a70ab1ff92547c4a1</t>
+          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19578699</t>
+          <t>L19556829</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2704,17 +2704,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785162974</t>
+          <t>1785172928</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1785335400</t>
+          <t>1785261600</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>10.758209</t>
+          <t>20.883534</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2731,31 +2731,39 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x79647a96f9215372245b4b53f196e63141ae86a1ea37ec3c520054924f339f07</t>
+          <t>0x0f77d19b1a11d1f8146d9103f3be3cbc4c3ff95c3bafe707daeb72cd0f7580ae</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>16.67997</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.2975</t>
+          <t>1.815</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>KF Drita</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -2763,27 +2771,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Apollon Limassol FC vs FC Dila Gori</t>
+          <t>KF Drita vs Floriana</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Apollon Limassol FC</t>
+          <t>KF Drita</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>FC Dila Gori</t>
+          <t>Floriana</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x000702f32390bc2acb841097855bbcf831db778647d8ef65ce0eb22695863bdc</t>
+          <t>0x09c0b1c15b6ea28d2c0107f466fade6e9caf4c75d4f55998d43c1e51232e5234</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19548403</t>
+          <t>L19556829</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2808,17 +2816,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785160034</t>
+          <t>1785172335</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1785258000</t>
+          <t>1785261600</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>24.470588</t>
+          <t>20.466221</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2835,54 +2843,46 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xc738fb5ab6b1a30b7c6c1ec2cd7f70095001f6e7c404f7f168998f3ce0923565</t>
+          <t>0x5e2fb7a1e61868dc87b64881470b8319cd876087d156626150e830a7cf27d189</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>281.53996</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.8588</t>
+          <t>1.285</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>UEFA Conference League</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Apollon Limassol FC vs FC Dila Gori</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
         <is>
           <t>Apollon Limassol FC</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>UEFA Conference League</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Apollon Limassol FC vs FC Dila Gori</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Apollon Limassol FC</t>
-        </is>
-      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>FC Dila Gori</t>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x6b053f472a4306388af8fe5ea15275295a0aae1b19a9f51e5b3c924cb4aacd4d</t>
+          <t>0x000702f32390bc2acb841097855bbcf831db778647d8ef65ce0eb22695863bdc</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785159837</t>
+          <t>1785171495</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>327.848571</t>
+          <t>294.035088</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2947,12 +2947,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x0b99d0d305609060f8495bfe5f8c95e1a0b399ad11cc9adf4f34153f68c97d71</t>
+          <t>0x00ae6c3a5ed7e25ed4adcc5d726b723762a6ddfb651274951dc984b567621eef</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.1025</t>
+          <t>1.1675</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>FC Dila Gori</t>
+          <t>Dukagjini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2987,27 +2987,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Apollon Limassol FC vs FC Dila Gori</t>
+          <t>Dukagjini vs FC Lugano</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Apollon Limassol FC</t>
+          <t>Dukagjini</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>FC Dila Gori</t>
+          <t>FC Lugano</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x66b17a5927b2a92224c605c32e8306f8dc8fabb6ccff81abfc5fbafb709f9a22</t>
+          <t>0xb4e6b34f8bd841e610d92a6e94ae60f508da52a98987521a70ab1ff92547c4a1</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19548403</t>
+          <t>L19578699</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3032,17 +3032,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785143243</t>
+          <t>1785164985</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1785258000</t>
+          <t>1785335400</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>9.853659</t>
+          <t>10.859701</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3059,12 +3059,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0xa2274ee0f4684479f0988ac6a5139708014cf026476c7cf9b37b3a416e7b5747</t>
+          <t>0x3d30d13f4f7532b8458d9fcb5fefaa11b7fdc084e05b8ea5921efdd1815c2b2e</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x1b1185C2A2d1Ec3CA592f5c21f52dD4aD449163f</t>
+          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1.802</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.0625</t>
+          <t>1.1675</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Paide Linnameeskond</t>
+          <t>Dukagjini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3099,27 +3099,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Zira FK vs Paide Linnameeskond</t>
+          <t>Dukagjini vs FC Lugano</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Zira FK</t>
+          <t>Dukagjini</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Paide Linnameeskond</t>
+          <t>FC Lugano</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0xc2274f3d5306fe3b7bf272b7cfce16894bf01595fd8fa3181858809c5afd887d</t>
+          <t>0xb4e6b34f8bd841e610d92a6e94ae60f508da52a98987521a70ab1ff92547c4a1</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19568228</t>
+          <t>L19578699</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3144,17 +3144,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785123628</t>
+          <t>1785162974</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1785427200</t>
+          <t>1785335400</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>10.758209</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3171,27 +3171,23 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x4b249266f4a129a90a4f4289f80efd22864a0b55a615a30c01a744c9e6fa007e</t>
+          <t>0x79647a96f9215372245b4b53f196e63141ae86a1ea37ec3c520054924f339f07</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.2463</t>
+          <t>1.2975</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3199,11 +3195,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>FC Spartak Trnava</t>
-        </is>
-      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -3211,27 +3203,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>FC CSKA Sofia 1948 vs FC Spartak Trnava</t>
+          <t>Apollon Limassol FC vs FC Dila Gori</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>FC CSKA Sofia 1948</t>
+          <t>Apollon Limassol FC</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>FC Spartak Trnava</t>
+          <t>FC Dila Gori</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0xe6d3ed6a25306fb2793f56682ed261dbde83f239772758b37aeecc6a973830a6</t>
+          <t>0x000702f32390bc2acb841097855bbcf831db778647d8ef65ce0eb22695863bdc</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19548391</t>
+          <t>L19548403</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3256,17 +3248,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785114331</t>
+          <t>1785160034</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1785259800</t>
+          <t>1785258000</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>20.020305</t>
+          <t>24.470588</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3283,31 +3275,39 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0xbcaacd1e8dc7d60abd70f28c7ffba7450e4c76519b53d45633047b2e308ce8df</t>
+          <t>0xc738fb5ab6b1a30b7c6c1ec2cd7f70095001f6e7c404f7f168998f3ce0923565</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
+          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>281.53996</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.835</t>
+          <t>1.8588</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Apollon Limassol FC</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -3315,27 +3315,27 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Dukagjini vs FC Lugano</t>
+          <t>Apollon Limassol FC vs FC Dila Gori</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Dukagjini</t>
+          <t>Apollon Limassol FC</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>FC Lugano</t>
+          <t>FC Dila Gori</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0xb4e6b34f8bd841e610d92a6e94ae60f508da52a98987521a70ab1ff92547c4a1</t>
+          <t>0x6b053f472a4306388af8fe5ea15275295a0aae1b19a9f51e5b3c924cb4aacd4d</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>L19578699</t>
+          <t>L19548403</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3360,17 +3360,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785108140</t>
+          <t>1785159837</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>1785335400</t>
+          <t>1785258000</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>5.02994</t>
+          <t>327.848571</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3387,23 +3387,27 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0xc4f834cac0960a0d1d3dfd961f4ed03d26a908325b0613bbc25d8271e7ea9596</t>
+          <t>0x0b99d0d305609060f8495bfe5f8c95e1a0b399ad11cc9adf4f34153f68c97d71</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.4062</t>
+          <t>1.1025</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3411,7 +3415,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>FC Dila Gori</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -3419,27 +3427,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>KF Drita vs Floriana</t>
+          <t>Apollon Limassol FC vs FC Dila Gori</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>KF Drita</t>
+          <t>Apollon Limassol FC</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Floriana</t>
+          <t>FC Dila Gori</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0xd80db7f29b1a9bf7479fe759db5892459ba76d2573c8028c682ca72ca26fa563</t>
+          <t>0x66b17a5927b2a92224c605c32e8306f8dc8fabb6ccff81abfc5fbafb709f9a22</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>L19556829</t>
+          <t>L19548403</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3464,17 +3472,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785102921</t>
+          <t>1785143243</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>1785261600</t>
+          <t>1785258000</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>9.853659</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3491,12 +3499,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x642cead4cce6abf15e60b5f101292963653928af192a53d61cf13be1f5735346</t>
+          <t>0xa2274ee0f4684479f0988ac6a5139708014cf026476c7cf9b37b3a416e7b5747</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x1b1185C2A2d1Ec3CA592f5c21f52dD4aD449163f</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3506,22 +3514,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>25.11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.0625</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SK Rapid Wien -2.5</t>
+          <t>Paide Linnameeskond</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3531,27 +3539,27 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>SK Rapid Wien vs FC Santa Coloma</t>
+          <t>Zira FK vs Paide Linnameeskond</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>SK Rapid Wien</t>
+          <t>Zira FK</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>FC Santa Coloma</t>
+          <t>Paide Linnameeskond</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x568429d159b17f3e17f83384554dcb4508d96942d411a493bfcdd9af2fd2df07</t>
+          <t>0xc2274f3d5306fe3b7bf272b7cfce16894bf01595fd8fa3181858809c5afd887d</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19558557</t>
+          <t>L19568228</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3576,17 +3584,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785100795</t>
+          <t>1785123628</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1785349800</t>
+          <t>1785427200</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>51.773196</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3603,31 +3611,39 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0xb86a834aa70af447f0675d386c1849b1c99fbb8415a4a0f57dedbfc3374369c8</t>
+          <t>0x4b249266f4a129a90a4f4289f80efd22864a0b55a615a30c01a744c9e6fa007e</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>10.74</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.2875</t>
+          <t>1.2463</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UEFA Conference League</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>FC Spartak Trnava</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -3635,27 +3651,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>KF Drita vs Floriana</t>
+          <t>FC CSKA Sofia 1948 vs FC Spartak Trnava</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>KF Drita</t>
+          <t>FC CSKA Sofia 1948</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Floriana</t>
+          <t>FC Spartak Trnava</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x74cee3640eed67802d8602418d415d7e5f881528425b4aded0a73b883c57f7c2</t>
+          <t>0xe6d3ed6a25306fb2793f56682ed261dbde83f239772758b37aeecc6a973830a6</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19556829</t>
+          <t>L19548391</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3680,17 +3696,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785068425</t>
+          <t>1785114331</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1785261600</t>
+          <t>1785259800</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>37.356522</t>
+          <t>20.020305</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3707,39 +3723,31 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x8004902c8df50fb0691955c2dde204aa37aea6ffc9f11cb60795a2b8862e7e34</t>
+          <t>0xbcaacd1e8dc7d60abd70f28c7ffba7450e4c76519b53d45633047b2e308ce8df</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.3188</t>
+          <t>1.835</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>KF Drita -1.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -3747,27 +3755,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>KF Drita vs Floriana</t>
+          <t>Dukagjini vs FC Lugano</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>KF Drita</t>
+          <t>Dukagjini</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Floriana</t>
+          <t>FC Lugano</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
+          <t>0xb4e6b34f8bd841e610d92a6e94ae60f508da52a98987521a70ab1ff92547c4a1</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>L19556829</t>
+          <t>L19578699</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3792,17 +3800,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785065693</t>
+          <t>1785108140</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1785261600</t>
+          <t>1785335400</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>5.301961</t>
+          <t>5.02994</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3819,39 +3827,31 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x9d52e065d77a1e2ffa07fa7250522f55f6a20661ddb8ab22b3656a5e5f518751</t>
+          <t>0xc4f834cac0960a0d1d3dfd961f4ed03d26a908325b0613bbc25d8271e7ea9596</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.3188</t>
+          <t>1.4062</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>KF Drita -1.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
+          <t>0xd80db7f29b1a9bf7479fe759db5892459ba76d2573c8028c682ca72ca26fa563</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785065679</t>
+          <t>1785102921</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3914,7 +3914,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>9.003922</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3931,12 +3931,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0xf072d053c048f056d7fa49c75da51e0772df0db003eaf3ddf341cb2fcc16c416</t>
+          <t>0x642cead4cce6abf15e60b5f101292963653928af192a53d61cf13be1f5735346</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3946,22 +3946,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>25.11</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.3188</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Asian Handicap (-2.5)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>KF Drita -1.5</t>
+          <t>SK Rapid Wien -2.5</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3971,27 +3971,27 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>KF Drita vs Floriana</t>
+          <t>SK Rapid Wien vs FC Santa Coloma</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>KF Drita</t>
+          <t>SK Rapid Wien</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Floriana</t>
+          <t>FC Santa Coloma</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
+          <t>0x568429d159b17f3e17f83384554dcb4508d96942d411a493bfcdd9af2fd2df07</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>L19556829</t>
+          <t>L19558557</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -4016,17 +4016,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785065519</t>
+          <t>1785100795</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1785261600</t>
+          <t>1785349800</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>14.117647</t>
+          <t>51.773196</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4043,39 +4043,31 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0xe1a18ecff833fc919588fdf2e22421fae16e5d31600f43cd14887e49499b233e</t>
+          <t>0xb86a834aa70af447f0675d386c1849b1c99fbb8415a4a0f57dedbfc3374369c8</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>10.74</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.3325</t>
+          <t>1.2875</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>KF Drita -1.5</t>
-        </is>
-      </c>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -4098,7 +4090,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
+          <t>0x74cee3640eed67802d8602418d415d7e5f881528425b4aded0a73b883c57f7c2</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4128,7 +4120,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785065131</t>
+          <t>1785068425</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4138,7 +4130,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>9.052632</t>
+          <t>37.356522</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4155,7 +4147,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x97e956b7b7cfe7d56ae2e8711191f397ae89244a032e763798c4b0021c72d481</t>
+          <t>0x8004902c8df50fb0691955c2dde204aa37aea6ffc9f11cb60795a2b8862e7e34</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4170,12 +4162,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.3325</t>
+          <t>1.3188</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4240,7 +4232,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785065030</t>
+          <t>1785065693</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4250,7 +4242,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>11.458647</t>
+          <t>5.301961</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4267,7 +4259,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x1b6d50b0b2f30b843c8afcdf1bdd77c807787389b518c0d0118f66c5c53154d1</t>
+          <t>0x9d52e065d77a1e2ffa07fa7250522f55f6a20661ddb8ab22b3656a5e5f518751</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4282,12 +4274,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.3325</t>
+          <t>1.3188</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4352,7 +4344,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785064974</t>
+          <t>1785065679</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4362,7 +4354,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>3.007519</t>
+          <t>9.003922</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4379,7 +4371,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x7de08a0243073e49c6e479dead7f166232ecd3480830513fb8953abf4d30f575</t>
+          <t>0xf072d053c048f056d7fa49c75da51e0772df0db003eaf3ddf341cb2fcc16c416</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4394,22 +4386,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.3188</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>KF Drita -1.5</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4419,27 +4411,27 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Riga FC vs Vardar</t>
+          <t>KF Drita vs Floriana</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Riga FC</t>
+          <t>KF Drita</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Floriana</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x3df545e9e324274c452d3611c5ff53dc80c8487fce47da81056d17c1b4257d63</t>
+          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>L19548393</t>
+          <t>L19556829</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4464,17 +4456,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785064838</t>
+          <t>1785065519</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1785258000</t>
+          <t>1785261600</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>13.333333</t>
+          <t>14.117647</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4491,7 +4483,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x98d07c005cea52102549964e374db87ed764bdb1840c7e4d0822a34701829208</t>
+          <t>0xe1a18ecff833fc919588fdf2e22421fae16e5d31600f43cd14887e49499b233e</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4499,15 +4491,19 @@
           <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>11.17999</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.3325</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4515,7 +4511,11 @@
           <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>KF Drita -1.5</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -4523,27 +4523,27 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Riga FC vs Vardar</t>
+          <t>KF Drita vs Floriana</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Riga FC</t>
+          <t>KF Drita</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Floriana</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x3ce984b8d5a4fd077770e33c33bd5244077e868cb901d0b9544238e72630158d</t>
+          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>L19548393</t>
+          <t>L19556829</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4568,17 +4568,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785064821</t>
+          <t>1785065131</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>1785258000</t>
+          <t>1785261600</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>22.304219</t>
+          <t>9.052632</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4595,7 +4595,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x90084d34df7f1c1dba6533a65ec3b370264b980f4ee2f405409784667aef3385</t>
+          <t>0x97e956b7b7cfe7d56ae2e8711191f397ae89244a032e763798c4b0021c72d481</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4610,12 +4610,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.3325</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785064821</t>
+          <t>1785065030</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>39.205882</t>
+          <t>11.458647</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4707,7 +4707,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0xd382b16331a33a8ef623d9f672b5567e3faaf5a8c56a6b1abbd17c5b3bf2447a</t>
+          <t>0x1b6d50b0b2f30b843c8afcdf1bdd77c807787389b518c0d0118f66c5c53154d1</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4722,22 +4722,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.3325</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>KF Drita -1.5</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4747,27 +4747,27 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Riga FC vs Vardar</t>
+          <t>KF Drita vs Floriana</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Riga FC</t>
+          <t>KF Drita</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Floriana</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x3df545e9e324274c452d3611c5ff53dc80c8487fce47da81056d17c1b4257d63</t>
+          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>L19548393</t>
+          <t>L19556829</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4792,17 +4792,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785064819</t>
+          <t>1785064974</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1785258000</t>
+          <t>1785261600</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>13.888889</t>
+          <t>3.007519</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4819,23 +4819,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0xc5ab66578686247686091622e73b8f1713617d5de6c2687bbf706bdd9a1c79eb</t>
+          <t>0x7de08a0243073e49c6e479dead7f166232ecd3480830513fb8953abf4d30f575</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0x594542a29FFceEAeaDD2e67955437c928B51B758</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.2637</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4843,7 +4847,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Vardar</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -4866,7 +4874,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x8f444d513fee4c89c59a5fac9732f2bdbc34c255f1e145e912b5e8d3864de79a</t>
+          <t>0x3df545e9e324274c452d3611c5ff53dc80c8487fce47da81056d17c1b4257d63</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4896,7 +4904,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785064813</t>
+          <t>1785064838</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4906,7 +4914,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>15.620853</t>
+          <t>13.333333</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4923,7 +4931,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x60648f843dfab3db80e7b11dc76bd422fb1242bf53219948830cbe4d1b29ee2e</t>
+          <t>0x98d07c005cea52102549964e374db87ed764bdb1840c7e4d0822a34701829208</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4931,54 +4939,46 @@
           <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>11.17999</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Riga FC vs Vardar</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Riga FC</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
         <is>
           <t>Vardar</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>UEFA Conference League</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Riga FC vs Vardar</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>Riga FC</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>Vardar</t>
-        </is>
-      </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x3df545e9e324274c452d3611c5ff53dc80c8487fce47da81056d17c1b4257d63</t>
+          <t>0x3ce984b8d5a4fd077770e33c33bd5244077e868cb901d0b9544238e72630158d</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1785064792</t>
+          <t>1785064821</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>15.444444</t>
+          <t>22.304219</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -5035,31 +5035,39 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0xd4092c9aa9c679f18a84f2d088ee1a8595762c53fd62d16b214a853eff1fde81</t>
+          <t>0x90084d34df7f1c1dba6533a65ec3b370264b980f4ee2f405409784667aef3385</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0x594542a29FFceEAeaDD2e67955437c928B51B758</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.2637</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>KF Drita -1.5</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -5067,27 +5075,27 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Riga FC vs Vardar</t>
+          <t>KF Drita vs Floriana</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Riga FC</t>
+          <t>KF Drita</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Floriana</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0x8f444d513fee4c89c59a5fac9732f2bdbc34c255f1e145e912b5e8d3864de79a</t>
+          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>L19548393</t>
+          <t>L19556829</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -5112,17 +5120,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1785064770</t>
+          <t>1785064821</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>1785258000</t>
+          <t>1785261600</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>13.914692</t>
+          <t>39.205882</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5139,102 +5147,534 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>0xd382b16331a33a8ef623d9f672b5567e3faaf5a8c56a6b1abbd17c5b3bf2447a</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Vardar</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Riga FC vs Vardar</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Riga FC</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Vardar</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>0x3df545e9e324274c452d3611c5ff53dc80c8487fce47da81056d17c1b4257d63</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>L19548393</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>1785064819</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>1785258000</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>13.888889</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>0xc5ab66578686247686091622e73b8f1713617d5de6c2687bbf706bdd9a1c79eb</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0x594542a29FFceEAeaDD2e67955437c928B51B758</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>4.12</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1.2637</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Riga FC vs Vardar</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Riga FC</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Vardar</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>0x8f444d513fee4c89c59a5fac9732f2bdbc34c255f1e145e912b5e8d3864de79a</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>L19548393</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>1785064813</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>1785258000</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>15.620853</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>0x60648f843dfab3db80e7b11dc76bd422fb1242bf53219948830cbe4d1b29ee2e</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Vardar</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Riga FC vs Vardar</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Riga FC</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Vardar</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>0x3df545e9e324274c452d3611c5ff53dc80c8487fce47da81056d17c1b4257d63</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>L19548393</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>1785064792</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>1785258000</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>15.444444</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>0xd4092c9aa9c679f18a84f2d088ee1a8595762c53fd62d16b214a853eff1fde81</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0x594542a29FFceEAeaDD2e67955437c928B51B758</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>3.67</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>1.2637</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Riga FC vs Vardar</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Riga FC</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Vardar</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0x8f444d513fee4c89c59a5fac9732f2bdbc34c255f1e145e912b5e8d3864de79a</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>L19548393</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>1785064770</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>1785258000</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>13.914692</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>0x3a9ab01f5b98d3619f0b7d9da475c1eabc0e13099a65941bdca6bd024e7991b6</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr">
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
         <is>
           <t>1.35</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>1.2637</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>UEFA Conference League</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
         <is>
           <t>Riga FC vs Vardar</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>Riga FC</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>Vardar</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>0x8f444d513fee4c89c59a5fac9732f2bdbc34c255f1e145e912b5e8d3864de79a</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>L19548393</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr">
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
         <is>
           <t>1785064754</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="S48" t="inlineStr">
         <is>
           <t>1785258000</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="T48" t="inlineStr">
         <is>
           <t>5.118483</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="U48" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr">
+      <c r="V48" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/UEFA Conference League/trades.xlsx
+++ b/data/sxbet/ligas/UEFA Conference League/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V48"/>
+  <dimension ref="A1:V54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,39 +531,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x3986ccac9da8fd1e2ec5eb9738ca6572eaf2aeb0920147dc7d704cdc2332d387</t>
+          <t>0x481c34ca369c9b4aa8872f25938f39dc6905259afbbd1102f5af4cd2f8dddc0b</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>20.05999</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.2888</t>
+          <t>1.6212</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -571,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Dukagjini vs FC Lugano</t>
+          <t>KF Drita vs Floriana</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Dukagjini</t>
+          <t>KF Drita</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>FC Lugano</t>
+          <t>Floriana</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x1f60001b19ddfc41630c6822a3d47aa8cf8680cef1620d6262024bae4641609b</t>
+          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19578699</t>
+          <t>L19556829</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785203409</t>
+          <t>1785218436</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785335400</t>
+          <t>1785261600</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>8.207792</t>
+          <t>32.289722</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,12 +635,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x6370d092d3abe8f1798c07306e22480e361fa8550787500075f06ff338a8ebd6</t>
+          <t>0x22c27416a938e147906cd612ac9b3121a0de10c5316b3a11cc0b6f4559f80043</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -658,39 +650,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>156.44</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.865</t>
+          <t>1.535</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>UEFA Conference League</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Riga FC vs Vardar</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>Riga FC</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>UEFA Conference League</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Riga FC vs Vardar</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Riga FC</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>Vardar</t>
@@ -698,7 +690,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xafe00bc468bca0fb7885d652a99b556a6d04f550216ba1d8550ec2732ba07436</t>
+          <t>0xdabc2e0010c9836a781baa7b8bad8b7a1626704507f2469cc1b6df80cf66cb5b</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -728,7 +720,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785202680</t>
+          <t>1785215182</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -738,7 +730,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>180.855491</t>
+          <t>10.542056</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,31 +747,39 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x1567a1c54e4cdeaac7c846b9591b4c414d90a932154ea48c45a261cffc97b3aa</t>
+          <t>0x3aff75dbd2985f267ba4e3975b26fb7ffb98b0a2c318e7524645d8893e1c3862</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.2888</t>
+          <t>1.5162</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>KF Drita -1</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -787,27 +787,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>SK Rapid Wien vs FC Santa Coloma</t>
+          <t>KF Drita vs Floriana</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>SK Rapid Wien</t>
+          <t>KF Drita</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>FC Santa Coloma</t>
+          <t>Floriana</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xcf09c10cb205e31ce255c67c424f013a3469ff7cc8e6cc11a0da2738847a6366</t>
+          <t>0x5412f1c6d1dfb833bab11103f4cc8d7e6df53302c4951b2ac6b6bec4e6f5ef02</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19558557</t>
+          <t>L19556829</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785199330</t>
+          <t>1785214601</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785349800</t>
+          <t>1785261600</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>17.316017</t>
+          <t>6.566586</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,12 +859,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x3e339f206f2088c795c4a0636e7271d6124859ebaa118a7c8a34e5622d9ca895</t>
+          <t>0x669bf318a8ee659722b80eafa91c88e0ca0afcb8e9f6152d70162d9288832efc</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -874,22 +874,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>12.23</t>
+          <t>13.56</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.3538</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Brann -2</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -899,27 +899,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Brann vs Universitatea Cluj</t>
+          <t>KF Drita vs Floriana</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>KF Drita</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Floriana</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x3014dbda6053f0222459758b857d801d076de578e0e8806b8a4ed056ec2508af</t>
+          <t>0xd8aa3e28f00c7e0870126fc41b4e5a4702fdb3c649aceea91936af957a7751ce</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19570054</t>
+          <t>L19556829</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -944,17 +944,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785197201</t>
+          <t>1785208604</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1785430800</t>
+          <t>1785261600</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>38.825397</t>
+          <t>38.332155</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,39 +971,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xe56a8509a245b02e123202b549bc14f2ca45ffdc40b5a7f4cd2c3c0747fde670</t>
+          <t>0x6985e96574fd153914b5a10b8bd8133b1f63ba1d4c31a0a88b57ae07ba939941</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>452.16992</t>
+          <t>26.6175</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.905</t>
+          <t>1.6338</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>UEFA Conference League</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Zira FK</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -1011,27 +1003,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Zira FK vs Paide Linnameeskond</t>
+          <t>KS Dinamo Tirana vs NK Aluminij</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Zira FK</t>
+          <t>KS Dinamo Tirana</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Paide Linnameeskond</t>
+          <t>NK Aluminij</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x56f6e71f9b6763e5ad84422820347dada907b51c1f11b22e4f4bca1e48f684c7</t>
+          <t>0x855c9fd81e9b5a4dcbc3ca7f5f4456f3da6e096a7928cad2b9abc0156ef53229</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19568228</t>
+          <t>L19568241</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1056,17 +1048,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785196074</t>
+          <t>1785206829</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1785427200</t>
+          <t>1785438000</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>499.635271</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1083,12 +1075,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xc2aab73ddffd7075b0f7b62fe496b81e8ff26c527fc6f8f306a4e978d3ed1efd</t>
+          <t>0xf66abd394921d5fe5ca2da5fb76396f6bc386e523dac693eeaefaf82c9bb3f6d</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x155C76202e45BE70c50bfeD7eAeA3B98e7716Ff7</t>
+          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1098,22 +1090,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.99999</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.7437</t>
+          <t>1.665</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (0.5)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Riga FC</t>
+          <t>Beitar Jerusalem +0.5</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1123,27 +1115,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Riga FC vs Vardar</t>
+          <t>Beitar Jerusalem vs AEK Larnaka</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Riga FC</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>AEK Larnaka</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x8f444d513fee4c89c59a5fac9732f2bdbc34c255f1e145e912b5e8d3864de79a</t>
+          <t>0x1ba797720a3cf1dab8b4ef41d19e7fe8423053372376b02544afdb7d56e05aa6</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19548393</t>
+          <t>L19568262</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1168,17 +1160,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785188484</t>
+          <t>1785206665</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1785258000</t>
+          <t>1785432600</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2.689062</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1195,12 +1187,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x145c09d9142ba2cbced4c8388017e78e14aa9401ee12d36d8129500f13df032e</t>
+          <t>0x3986ccac9da8fd1e2ec5eb9738ca6572eaf2aeb0920147dc7d704cdc2332d387</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1210,22 +1202,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>54.69828</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.5288</t>
+          <t>1.2888</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>KF Drita -1</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1235,27 +1227,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>KF Drita vs Floriana</t>
+          <t>Dukagjini vs FC Lugano</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>KF Drita</t>
+          <t>Dukagjini</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Floriana</t>
+          <t>FC Lugano</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x5412f1c6d1dfb833bab11103f4cc8d7e6df53302c4951b2ac6b6bec4e6f5ef02</t>
+          <t>0x1f60001b19ddfc41630c6822a3d47aa8cf8680cef1620d6262024bae4641609b</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19556829</t>
+          <t>L19578699</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1280,17 +1272,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785188240</t>
+          <t>1785203409</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1785261600</t>
+          <t>1785335400</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>103.448284</t>
+          <t>8.207792</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1307,7 +1299,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x9cf4023491039f5bb7dac0df23c846094dd01f9dbee02e57798e16c37d85f644</t>
+          <t>0x6370d092d3abe8f1798c07306e22480e361fa8550787500075f06ff338a8ebd6</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1322,22 +1314,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>156.44</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.395</t>
+          <t>1.865</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>UEFA Conference League</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Riga FC</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1362,7 +1354,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x4b27547b8aa1ca6be4f6c92d7d7529a6f2db813e76b6e813d964bae73b66325b</t>
+          <t>0xafe00bc468bca0fb7885d652a99b556a6d04f550216ba1d8550ec2732ba07436</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1392,7 +1384,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785187553</t>
+          <t>1785202680</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1402,7 +1394,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>6.708861</t>
+          <t>180.855491</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1419,39 +1411,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xc7e6d7d15508ccc8392a870d6681e7b64fd2e6038be310a8a884315b6a1c961c</t>
+          <t>0x1567a1c54e4cdeaac7c846b9591b4c414d90a932154ea48c45a261cffc97b3aa</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x1b1185C2A2d1Ec3CA592f5c21f52dD4aD449163f</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.175</t>
+          <t>1.2888</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -1459,27 +1443,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Riga FC vs Vardar</t>
+          <t>SK Rapid Wien vs FC Santa Coloma</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Riga FC</t>
+          <t>SK Rapid Wien</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>FC Santa Coloma</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x493fb5a9e01ebf84f758d2393d26a55e30244a3f9d8b15eb25d6f79450841850</t>
+          <t>0xcf09c10cb205e31ce255c67c424f013a3469ff7cc8e6cc11a0da2738847a6366</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19548393</t>
+          <t>L19558557</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1504,17 +1488,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785186255</t>
+          <t>1785199330</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1785258000</t>
+          <t>1785349800</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>142.857143</t>
+          <t>17.316017</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1531,12 +1515,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x97bc06ccc193bcef116dbd3167a750fb9715b73503439c03d33582d95f59a027</t>
+          <t>0x3e339f206f2088c795c4a0636e7271d6124859ebaa118a7c8a34e5622d9ca895</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x1b1185C2A2d1Ec3CA592f5c21f52dD4aD449163f</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1546,22 +1530,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>12.23</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.1125</t>
+          <t>1.315</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-2)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>FC Dila Gori</t>
+          <t>Brann -2</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1571,27 +1555,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Apollon Limassol FC vs FC Dila Gori</t>
+          <t>Brann vs Universitatea Cluj</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Apollon Limassol FC</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>FC Dila Gori</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x66b17a5927b2a92224c605c32e8306f8dc8fabb6ccff81abfc5fbafb709f9a22</t>
+          <t>0x3014dbda6053f0222459758b857d801d076de578e0e8806b8a4ed056ec2508af</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19548403</t>
+          <t>L19570054</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1616,17 +1600,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785186085</t>
+          <t>1785197201</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1785258000</t>
+          <t>1785430800</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>222.222222</t>
+          <t>38.825397</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1643,31 +1627,39 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xa1b38b181df840d94fccfceb9be5cfd1c9808b3603eb40e8e856fea5c36c33f0</t>
+          <t>0xe56a8509a245b02e123202b549bc14f2ca45ffdc40b5a7f4cd2c3c0747fde670</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>452.16992</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.905</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Zira FK</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -1675,27 +1667,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>GKS Katowice vs MSK Zilina</t>
+          <t>Zira FK vs Paide Linnameeskond</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Zira FK</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>MSK Zilina</t>
+          <t>Paide Linnameeskond</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x17ea810aed80a43d53397b03233a18bc09fd2fccf8db1130f11e12f7f95c91e7</t>
+          <t>0x56f6e71f9b6763e5ad84422820347dada907b51c1f11b22e4f4bca1e48f684c7</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19568244</t>
+          <t>L19568228</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1720,17 +1712,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785184086</t>
+          <t>1785196074</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785427200</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>499.635271</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1747,12 +1739,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xe5723419c39bca85b784eb615a725a9a26a5c239d525f82b27535463ba9d9f88</t>
+          <t>0xc2aab73ddffd7075b0f7b62fe496b81e8ff26c527fc6f8f306a4e978d3ed1efd</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0x155C76202e45BE70c50bfeD7eAeA3B98e7716Ff7</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1762,22 +1754,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>203.62057</t>
+          <t>1.99999</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.8838</t>
+          <t>1.7437</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>UEFA Conference League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Riga FC</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1787,27 +1779,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Panathinaikos vs Paksi SE</t>
+          <t>Riga FC vs Vardar</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Riga FC</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x9747c98c82c1e1aeebd441f71649b575a324218f5bb412402cb90fb1639eb40f</t>
+          <t>0x8f444d513fee4c89c59a5fac9732f2bdbc34c255f1e145e912b5e8d3864de79a</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19568307</t>
+          <t>L19548393</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1832,17 +1824,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785178979</t>
+          <t>1785188484</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785258000</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>230.405171</t>
+          <t>2.689062</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1859,31 +1851,39 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x9d2c4725405077ca1bceaff142e2ed3d4e9ff5d3b138a2f49b31afb87c9fa625</t>
+          <t>0x145c09d9142ba2cbced4c8388017e78e14aa9401ee12d36d8129500f13df032e</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>25.92059</t>
+          <t>54.69828</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.1125</t>
+          <t>1.5288</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UEFA Conference League</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>KF Drita -1</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -1891,27 +1891,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Panathinaikos vs Paksi SE</t>
+          <t>KF Drita vs Floriana</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>KF Drita</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Floriana</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x9747c98c82c1e1aeebd441f71649b575a324218f5bb412402cb90fb1639eb40f</t>
+          <t>0x5412f1c6d1dfb833bab11103f4cc8d7e6df53302c4951b2ac6b6bec4e6f5ef02</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19568307</t>
+          <t>L19556829</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1936,17 +1936,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785178979</t>
+          <t>1785188240</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1785436200</t>
+          <t>1785261600</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>230.405244</t>
+          <t>103.448284</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1963,7 +1963,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x09e55e9944cfa459297c6a9f1bd507159b106de1f3987c8394a2b0fd67f3ba3b</t>
+          <t>0x9cf4023491039f5bb7dac0df23c846094dd01f9dbee02e57798e16c37d85f644</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1978,22 +1978,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>82.92</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.395</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>UEFA Conference League</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>FC CSKA Sofia 1948</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2003,27 +2003,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>FC CSKA Sofia 1948 vs FC Spartak Trnava</t>
+          <t>Riga FC vs Vardar</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>FC CSKA Sofia 1948</t>
+          <t>Riga FC</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>FC Spartak Trnava</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x0f0e918dc732446e9ce6f03b0a5b34d1a075bcff9ed3e2ca33563b8eea52d345</t>
+          <t>0x4b27547b8aa1ca6be4f6c92d7d7529a6f2db813e76b6e813d964bae73b66325b</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19548391</t>
+          <t>L19548393</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2048,17 +2048,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785178520</t>
+          <t>1785187553</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1785259800</t>
+          <t>1785258000</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>123.761194</t>
+          <t>6.708861</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2075,12 +2075,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xff24d53e0d12e00d437b591e035e6a102c9ec294448637ea1d827288ccdfd669</t>
+          <t>0xc7e6d7d15508ccc8392a870d6681e7b64fd2e6038be310a8a884315b6a1c961c</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x1b1185C2A2d1Ec3CA592f5c21f52dD4aD449163f</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2090,22 +2090,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>32.29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.7025</t>
+          <t>1.175</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>UEFA Conference League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>FC CSKA Sofia 1948</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2115,27 +2115,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>FC CSKA Sofia 1948 vs FC Spartak Trnava</t>
+          <t>Riga FC vs Vardar</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>FC CSKA Sofia 1948</t>
+          <t>Riga FC</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>FC Spartak Trnava</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x0f0e918dc732446e9ce6f03b0a5b34d1a075bcff9ed3e2ca33563b8eea52d345</t>
+          <t>0x493fb5a9e01ebf84f758d2393d26a55e30244a3f9d8b15eb25d6f79450841850</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19548391</t>
+          <t>L19548393</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2160,17 +2160,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785178483</t>
+          <t>1785186255</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1785259800</t>
+          <t>1785258000</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>45.964413</t>
+          <t>142.857143</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2187,23 +2187,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xa2145f7f39e67fd641cdc795fb35638f93441f575672f474dcbb129d212b2071</t>
+          <t>0x97bc06ccc193bcef116dbd3167a750fb9715b73503439c03d33582d95f59a027</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>0x1b1185C2A2d1Ec3CA592f5c21f52dD4aD449163f</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>282.04998</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.8675</t>
+          <t>1.1125</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2211,7 +2215,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>FC Dila Gori</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -2219,27 +2227,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>KF Drita vs Floriana</t>
+          <t>Apollon Limassol FC vs FC Dila Gori</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>KF Drita</t>
+          <t>Apollon Limassol FC</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Floriana</t>
+          <t>FC Dila Gori</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xd67d116960d6336d573e0df6e68fbc4925de62b55e56c443ceca3b50f83a0f30</t>
+          <t>0x66b17a5927b2a92224c605c32e8306f8dc8fabb6ccff81abfc5fbafb709f9a22</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19556829</t>
+          <t>L19548403</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2264,17 +2272,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785178247</t>
+          <t>1785186085</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1785261600</t>
+          <t>1785258000</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>325.12966</t>
+          <t>222.222222</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2291,39 +2299,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x81f3111a3468acf1de52d30ac0604c9ee06fc1a0787546268f23addd010feff2</t>
+          <t>0xa1b38b181df840d94fccfceb9be5cfd1c9808b3603eb40e8e856fea5c36c33f0</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>101.96</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.8013</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>UEFA Conference League</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>KF Drita</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -2331,27 +2331,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>KF Drita vs Floriana</t>
+          <t>GKS Katowice vs MSK Zilina</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>KF Drita</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Floriana</t>
+          <t>MSK Zilina</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x09c0b1c15b6ea28d2c0107f466fade6e9caf4c75d4f55998d43c1e51232e5234</t>
+          <t>0x17ea810aed80a43d53397b03233a18bc09fd2fccf8db1130f11e12f7f95c91e7</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19556829</t>
+          <t>L19568244</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2376,17 +2376,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785175205</t>
+          <t>1785184086</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1785261600</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>127.25117</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2403,12 +2403,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xe051c5dca29cf389a307215b76298a2e45bf4baccb56422aafc9a3c300c155dd</t>
+          <t>0xe5723419c39bca85b784eb615a725a9a26a5c239d525f82b27535463ba9d9f88</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>18.61997</t>
+          <t>203.62057</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.8013</t>
+          <t>1.8838</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>KF Drita</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2443,27 +2443,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>KF Drita vs Floriana</t>
+          <t>Panathinaikos vs Paksi SE</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>KF Drita</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Floriana</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x09c0b1c15b6ea28d2c0107f466fade6e9caf4c75d4f55998d43c1e51232e5234</t>
+          <t>0x9747c98c82c1e1aeebd441f71649b575a324218f5bb412402cb90fb1639eb40f</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19556829</t>
+          <t>L19568307</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2488,17 +2488,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785174328</t>
+          <t>1785178979</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1785261600</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>23.238652</t>
+          <t>230.405171</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2515,27 +2515,23 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xdaaf4df1704b396668995377988eea9bc6831ef12573030f333c949030199143</t>
+          <t>0x9d2c4725405077ca1bceaff142e2ed3d4e9ff5d3b138a2f49b31afb87c9fa625</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>21.48999</t>
+          <t>25.92059</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.8013</t>
+          <t>1.1125</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2543,11 +2539,7 @@
           <t>UEFA Conference League</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>KF Drita</t>
-        </is>
-      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -2555,27 +2547,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>KF Drita vs Floriana</t>
+          <t>Panathinaikos vs Paksi SE</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>KF Drita</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Floriana</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x09c0b1c15b6ea28d2c0107f466fade6e9caf4c75d4f55998d43c1e51232e5234</t>
+          <t>0x9747c98c82c1e1aeebd441f71649b575a324218f5bb412402cb90fb1639eb40f</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19556829</t>
+          <t>L19568307</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2600,17 +2592,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785174135</t>
+          <t>1785178979</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1785261600</t>
+          <t>1785436200</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>26.82058</t>
+          <t>230.405244</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2627,31 +2619,39 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x94f8a12cc97509762210745df2b56516620b6491bd6d10909e3496335a55dd21</t>
+          <t>0x09e55e9944cfa459297c6a9f1bd507159b106de1f3987c8394a2b0fd67f3ba3b</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x960070fC76573ff9c086dB473f99CA99ea914dd6</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>82.92</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.6225</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>FC CSKA Sofia 1948</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -2659,27 +2659,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>KF Drita vs Floriana</t>
+          <t>FC CSKA Sofia 1948 vs FC Spartak Trnava</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>KF Drita</t>
+          <t>FC CSKA Sofia 1948</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Floriana</t>
+          <t>FC Spartak Trnava</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
+          <t>0x0f0e918dc732446e9ce6f03b0a5b34d1a075bcff9ed3e2ca33563b8eea52d345</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19556829</t>
+          <t>L19548391</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2704,17 +2704,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785172928</t>
+          <t>1785178520</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1785261600</t>
+          <t>1785259800</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>20.883534</t>
+          <t>123.761194</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2731,12 +2731,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x0f77d19b1a11d1f8146d9103f3be3cbc4c3ff95c3bafe707daeb72cd0f7580ae</t>
+          <t>0xff24d53e0d12e00d437b591e035e6a102c9ec294448637ea1d827288ccdfd669</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2746,12 +2746,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>16.67997</t>
+          <t>32.29</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.815</t>
+          <t>1.7025</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>KF Drita</t>
+          <t>FC CSKA Sofia 1948</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2771,27 +2771,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>KF Drita vs Floriana</t>
+          <t>FC CSKA Sofia 1948 vs FC Spartak Trnava</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>KF Drita</t>
+          <t>FC CSKA Sofia 1948</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Floriana</t>
+          <t>FC Spartak Trnava</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x09c0b1c15b6ea28d2c0107f466fade6e9caf4c75d4f55998d43c1e51232e5234</t>
+          <t>0x0f0e918dc732446e9ce6f03b0a5b34d1a075bcff9ed3e2ca33563b8eea52d345</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19556829</t>
+          <t>L19548391</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2816,17 +2816,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785172335</t>
+          <t>1785178483</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1785261600</t>
+          <t>1785259800</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>20.466221</t>
+          <t>45.964413</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2843,23 +2843,23 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x5e2fb7a1e61868dc87b64881470b8319cd876087d156626150e830a7cf27d189</t>
+          <t>0xa2145f7f39e67fd641cdc795fb35638f93441f575672f474dcbb129d212b2071</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>282.04998</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.285</t>
+          <t>1.8675</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2875,27 +2875,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Apollon Limassol FC vs FC Dila Gori</t>
+          <t>KF Drita vs Floriana</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Apollon Limassol FC</t>
+          <t>KF Drita</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>FC Dila Gori</t>
+          <t>Floriana</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x000702f32390bc2acb841097855bbcf831db778647d8ef65ce0eb22695863bdc</t>
+          <t>0xd67d116960d6336d573e0df6e68fbc4925de62b55e56c443ceca3b50f83a0f30</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19548403</t>
+          <t>L19556829</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2920,17 +2920,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785171495</t>
+          <t>1785178247</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1785258000</t>
+          <t>1785261600</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>294.035088</t>
+          <t>325.12966</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2947,12 +2947,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x00ae6c3a5ed7e25ed4adcc5d726b723762a6ddfb651274951dc984b567621eef</t>
+          <t>0x81f3111a3468acf1de52d30ac0604c9ee06fc1a0787546268f23addd010feff2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2962,22 +2962,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>101.96</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.1675</t>
+          <t>1.8013</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>UEFA Conference League</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dukagjini</t>
+          <t>KF Drita</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2987,27 +2987,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Dukagjini vs FC Lugano</t>
+          <t>KF Drita vs Floriana</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Dukagjini</t>
+          <t>KF Drita</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>FC Lugano</t>
+          <t>Floriana</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0xb4e6b34f8bd841e610d92a6e94ae60f508da52a98987521a70ab1ff92547c4a1</t>
+          <t>0x09c0b1c15b6ea28d2c0107f466fade6e9caf4c75d4f55998d43c1e51232e5234</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19578699</t>
+          <t>L19556829</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3032,17 +3032,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785164985</t>
+          <t>1785175205</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1785335400</t>
+          <t>1785261600</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>10.859701</t>
+          <t>127.25117</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3059,12 +3059,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x3d30d13f4f7532b8458d9fcb5fefaa11b7fdc084e05b8ea5921efdd1815c2b2e</t>
+          <t>0xe051c5dca29cf389a307215b76298a2e45bf4baccb56422aafc9a3c300c155dd</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3074,22 +3074,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.802</t>
+          <t>18.61997</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.1675</t>
+          <t>1.8013</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>UEFA Conference League</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dukagjini</t>
+          <t>KF Drita</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3099,27 +3099,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Dukagjini vs FC Lugano</t>
+          <t>KF Drita vs Floriana</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Dukagjini</t>
+          <t>KF Drita</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>FC Lugano</t>
+          <t>Floriana</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0xb4e6b34f8bd841e610d92a6e94ae60f508da52a98987521a70ab1ff92547c4a1</t>
+          <t>0x09c0b1c15b6ea28d2c0107f466fade6e9caf4c75d4f55998d43c1e51232e5234</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19578699</t>
+          <t>L19556829</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3144,17 +3144,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785162974</t>
+          <t>1785174328</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1785335400</t>
+          <t>1785261600</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>10.758209</t>
+          <t>23.238652</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3171,31 +3171,39 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x79647a96f9215372245b4b53f196e63141ae86a1ea37ec3c520054924f339f07</t>
+          <t>0xdaaf4df1704b396668995377988eea9bc6831ef12573030f333c949030199143</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>21.48999</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.2975</t>
+          <t>1.8013</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>KF Drita</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -3203,27 +3211,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Apollon Limassol FC vs FC Dila Gori</t>
+          <t>KF Drita vs Floriana</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Apollon Limassol FC</t>
+          <t>KF Drita</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>FC Dila Gori</t>
+          <t>Floriana</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x000702f32390bc2acb841097855bbcf831db778647d8ef65ce0eb22695863bdc</t>
+          <t>0x09c0b1c15b6ea28d2c0107f466fade6e9caf4c75d4f55998d43c1e51232e5234</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19548403</t>
+          <t>L19556829</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3248,17 +3256,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785160034</t>
+          <t>1785174135</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1785258000</t>
+          <t>1785261600</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>24.470588</t>
+          <t>26.82058</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3275,39 +3283,31 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0xc738fb5ab6b1a30b7c6c1ec2cd7f70095001f6e7c404f7f168998f3ce0923565</t>
+          <t>0x94f8a12cc97509762210745df2b56516620b6491bd6d10909e3496335a55dd21</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x960070fC76573ff9c086dB473f99CA99ea914dd6</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>281.53996</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.8588</t>
+          <t>1.6225</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>UEFA Conference League</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Apollon Limassol FC</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -3315,27 +3315,27 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Apollon Limassol FC vs FC Dila Gori</t>
+          <t>KF Drita vs Floriana</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Apollon Limassol FC</t>
+          <t>KF Drita</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>FC Dila Gori</t>
+          <t>Floriana</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x6b053f472a4306388af8fe5ea15275295a0aae1b19a9f51e5b3c924cb4aacd4d</t>
+          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>L19548403</t>
+          <t>L19556829</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3360,17 +3360,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785159837</t>
+          <t>1785172928</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>1785258000</t>
+          <t>1785261600</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>327.848571</t>
+          <t>20.883534</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3387,12 +3387,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x0b99d0d305609060f8495bfe5f8c95e1a0b399ad11cc9adf4f34153f68c97d71</t>
+          <t>0x0f77d19b1a11d1f8146d9103f3be3cbc4c3ff95c3bafe707daeb72cd0f7580ae</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3402,22 +3402,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>16.67997</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.1025</t>
+          <t>1.815</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>UEFA Conference League</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>FC Dila Gori</t>
+          <t>KF Drita</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3427,27 +3427,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Apollon Limassol FC vs FC Dila Gori</t>
+          <t>KF Drita vs Floriana</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Apollon Limassol FC</t>
+          <t>KF Drita</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>FC Dila Gori</t>
+          <t>Floriana</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x66b17a5927b2a92224c605c32e8306f8dc8fabb6ccff81abfc5fbafb709f9a22</t>
+          <t>0x09c0b1c15b6ea28d2c0107f466fade6e9caf4c75d4f55998d43c1e51232e5234</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>L19548403</t>
+          <t>L19556829</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3472,17 +3472,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785143243</t>
+          <t>1785172335</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>1785258000</t>
+          <t>1785261600</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>9.853659</t>
+          <t>20.466221</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3499,27 +3499,23 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0xa2274ee0f4684479f0988ac6a5139708014cf026476c7cf9b37b3a416e7b5747</t>
+          <t>0x5e2fb7a1e61868dc87b64881470b8319cd876087d156626150e830a7cf27d189</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x1b1185C2A2d1Ec3CA592f5c21f52dD4aD449163f</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.0625</t>
+          <t>1.285</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3527,11 +3523,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Paide Linnameeskond</t>
-        </is>
-      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -3539,27 +3531,27 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Zira FK vs Paide Linnameeskond</t>
+          <t>Apollon Limassol FC vs FC Dila Gori</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Zira FK</t>
+          <t>Apollon Limassol FC</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Paide Linnameeskond</t>
+          <t>FC Dila Gori</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0xc2274f3d5306fe3b7bf272b7cfce16894bf01595fd8fa3181858809c5afd887d</t>
+          <t>0x000702f32390bc2acb841097855bbcf831db778647d8ef65ce0eb22695863bdc</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19568228</t>
+          <t>L19548403</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3584,17 +3576,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785123628</t>
+          <t>1785171495</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1785427200</t>
+          <t>1785258000</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>294.035088</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3611,12 +3603,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x4b249266f4a129a90a4f4289f80efd22864a0b55a615a30c01a744c9e6fa007e</t>
+          <t>0x00ae6c3a5ed7e25ed4adcc5d726b723762a6ddfb651274951dc984b567621eef</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3626,12 +3618,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.2463</t>
+          <t>1.1675</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3641,7 +3633,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>FC Spartak Trnava</t>
+          <t>Dukagjini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3651,27 +3643,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>FC CSKA Sofia 1948 vs FC Spartak Trnava</t>
+          <t>Dukagjini vs FC Lugano</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>FC CSKA Sofia 1948</t>
+          <t>Dukagjini</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>FC Spartak Trnava</t>
+          <t>FC Lugano</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0xe6d3ed6a25306fb2793f56682ed261dbde83f239772758b37aeecc6a973830a6</t>
+          <t>0xb4e6b34f8bd841e610d92a6e94ae60f508da52a98987521a70ab1ff92547c4a1</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19548391</t>
+          <t>L19578699</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3696,17 +3688,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785114331</t>
+          <t>1785164985</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1785259800</t>
+          <t>1785335400</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>20.020305</t>
+          <t>10.859701</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3723,23 +3715,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0xbcaacd1e8dc7d60abd70f28c7ffba7450e4c76519b53d45633047b2e308ce8df</t>
+          <t>0x3d30d13f4f7532b8458d9fcb5fefaa11b7fdc084e05b8ea5921efdd1815c2b2e</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>1.802</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.835</t>
+          <t>1.1675</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3747,7 +3743,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Dukagjini</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785108140</t>
+          <t>1785162974</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>5.02994</t>
+          <t>10.758209</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3827,7 +3827,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0xc4f834cac0960a0d1d3dfd961f4ed03d26a908325b0613bbc25d8271e7ea9596</t>
+          <t>0x79647a96f9215372245b4b53f196e63141ae86a1ea37ec3c520054924f339f07</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3838,12 +3838,12 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.4062</t>
+          <t>1.2975</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3859,27 +3859,27 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>KF Drita vs Floriana</t>
+          <t>Apollon Limassol FC vs FC Dila Gori</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>KF Drita</t>
+          <t>Apollon Limassol FC</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Floriana</t>
+          <t>FC Dila Gori</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0xd80db7f29b1a9bf7479fe759db5892459ba76d2573c8028c682ca72ca26fa563</t>
+          <t>0x000702f32390bc2acb841097855bbcf831db778647d8ef65ce0eb22695863bdc</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>L19556829</t>
+          <t>L19548403</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3904,17 +3904,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785102921</t>
+          <t>1785160034</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1785261600</t>
+          <t>1785258000</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>24.470588</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3931,12 +3931,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x642cead4cce6abf15e60b5f101292963653928af192a53d61cf13be1f5735346</t>
+          <t>0xc738fb5ab6b1a30b7c6c1ec2cd7f70095001f6e7c404f7f168998f3ce0923565</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3946,22 +3946,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>25.11</t>
+          <t>281.53996</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.8588</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
+          <t>UEFA Conference League</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SK Rapid Wien -2.5</t>
+          <t>Apollon Limassol FC</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3971,27 +3971,27 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>SK Rapid Wien vs FC Santa Coloma</t>
+          <t>Apollon Limassol FC vs FC Dila Gori</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>SK Rapid Wien</t>
+          <t>Apollon Limassol FC</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>FC Santa Coloma</t>
+          <t>FC Dila Gori</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x568429d159b17f3e17f83384554dcb4508d96942d411a493bfcdd9af2fd2df07</t>
+          <t>0x6b053f472a4306388af8fe5ea15275295a0aae1b19a9f51e5b3c924cb4aacd4d</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>L19558557</t>
+          <t>L19548403</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -4016,17 +4016,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785100795</t>
+          <t>1785159837</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1785349800</t>
+          <t>1785258000</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>51.773196</t>
+          <t>327.848571</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4043,31 +4043,39 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0xb86a834aa70af447f0675d386c1849b1c99fbb8415a4a0f57dedbfc3374369c8</t>
+          <t>0x0b99d0d305609060f8495bfe5f8c95e1a0b399ad11cc9adf4f34153f68c97d71</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>10.74</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.2875</t>
+          <t>1.1025</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>UEFA Conference League</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>FC Dila Gori</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -4075,27 +4083,27 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>KF Drita vs Floriana</t>
+          <t>Apollon Limassol FC vs FC Dila Gori</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>KF Drita</t>
+          <t>Apollon Limassol FC</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Floriana</t>
+          <t>FC Dila Gori</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x74cee3640eed67802d8602418d415d7e5f881528425b4aded0a73b883c57f7c2</t>
+          <t>0x66b17a5927b2a92224c605c32e8306f8dc8fabb6ccff81abfc5fbafb709f9a22</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>L19556829</t>
+          <t>L19548403</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4120,17 +4128,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785068425</t>
+          <t>1785143243</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1785261600</t>
+          <t>1785258000</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>37.356522</t>
+          <t>9.853659</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4147,12 +4155,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x8004902c8df50fb0691955c2dde204aa37aea6ffc9f11cb60795a2b8862e7e34</t>
+          <t>0xa2274ee0f4684479f0988ac6a5139708014cf026476c7cf9b37b3a416e7b5747</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x1b1185C2A2d1Ec3CA592f5c21f52dD4aD449163f</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4162,22 +4170,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.3188</t>
+          <t>1.0625</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>KF Drita -1.5</t>
+          <t>Paide Linnameeskond</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4187,27 +4195,27 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>KF Drita vs Floriana</t>
+          <t>Zira FK vs Paide Linnameeskond</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>KF Drita</t>
+          <t>Zira FK</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Floriana</t>
+          <t>Paide Linnameeskond</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
+          <t>0xc2274f3d5306fe3b7bf272b7cfce16894bf01595fd8fa3181858809c5afd887d</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>L19556829</t>
+          <t>L19568228</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4232,17 +4240,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785065693</t>
+          <t>1785123628</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>1785261600</t>
+          <t>1785427200</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>5.301961</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4259,7 +4267,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x9d52e065d77a1e2ffa07fa7250522f55f6a20661ddb8ab22b3656a5e5f518751</t>
+          <t>0x4b249266f4a129a90a4f4289f80efd22864a0b55a615a30c01a744c9e6fa007e</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4274,22 +4282,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.3188</t>
+          <t>1.2463</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>KF Drita -1.5</t>
+          <t>FC Spartak Trnava</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4299,27 +4307,27 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>KF Drita vs Floriana</t>
+          <t>FC CSKA Sofia 1948 vs FC Spartak Trnava</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>KF Drita</t>
+          <t>FC CSKA Sofia 1948</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Floriana</t>
+          <t>FC Spartak Trnava</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
+          <t>0xe6d3ed6a25306fb2793f56682ed261dbde83f239772758b37aeecc6a973830a6</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>L19556829</t>
+          <t>L19548391</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4344,17 +4352,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785065679</t>
+          <t>1785114331</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>1785261600</t>
+          <t>1785259800</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>9.003922</t>
+          <t>20.020305</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4371,39 +4379,31 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0xf072d053c048f056d7fa49c75da51e0772df0db003eaf3ddf341cb2fcc16c416</t>
+          <t>0xbcaacd1e8dc7d60abd70f28c7ffba7450e4c76519b53d45633047b2e308ce8df</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.3188</t>
+          <t>1.835</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>KF Drita -1.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -4411,27 +4411,27 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>KF Drita vs Floriana</t>
+          <t>Dukagjini vs FC Lugano</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>KF Drita</t>
+          <t>Dukagjini</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Floriana</t>
+          <t>FC Lugano</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
+          <t>0xb4e6b34f8bd841e610d92a6e94ae60f508da52a98987521a70ab1ff92547c4a1</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>L19556829</t>
+          <t>L19578699</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4456,17 +4456,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785065519</t>
+          <t>1785108140</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1785261600</t>
+          <t>1785335400</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>14.117647</t>
+          <t>5.02994</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4483,39 +4483,31 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0xe1a18ecff833fc919588fdf2e22421fae16e5d31600f43cd14887e49499b233e</t>
+          <t>0xc4f834cac0960a0d1d3dfd961f4ed03d26a908325b0613bbc25d8271e7ea9596</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.3325</t>
+          <t>1.4062</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>KF Drita -1.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -4538,7 +4530,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
+          <t>0xd80db7f29b1a9bf7479fe759db5892459ba76d2573c8028c682ca72ca26fa563</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4568,7 +4560,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785065131</t>
+          <t>1785102921</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4578,7 +4570,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>9.052632</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4595,12 +4587,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x97e956b7b7cfe7d56ae2e8711191f397ae89244a032e763798c4b0021c72d481</t>
+          <t>0x642cead4cce6abf15e60b5f101292963653928af192a53d61cf13be1f5735346</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4610,22 +4602,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>25.11</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.3325</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Asian Handicap (-2.5)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>KF Drita -1.5</t>
+          <t>SK Rapid Wien -2.5</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4635,27 +4627,27 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>KF Drita vs Floriana</t>
+          <t>SK Rapid Wien vs FC Santa Coloma</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>KF Drita</t>
+          <t>SK Rapid Wien</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Floriana</t>
+          <t>FC Santa Coloma</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
+          <t>0x568429d159b17f3e17f83384554dcb4508d96942d411a493bfcdd9af2fd2df07</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>L19556829</t>
+          <t>L19558557</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4680,17 +4672,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785065030</t>
+          <t>1785100795</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>1785261600</t>
+          <t>1785349800</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>11.458647</t>
+          <t>51.773196</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4707,39 +4699,31 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x1b6d50b0b2f30b843c8afcdf1bdd77c807787389b518c0d0118f66c5c53154d1</t>
+          <t>0xb86a834aa70af447f0675d386c1849b1c99fbb8415a4a0f57dedbfc3374369c8</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10.74</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.3325</t>
+          <t>1.2875</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>KF Drita -1.5</t>
-        </is>
-      </c>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -4762,7 +4746,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
+          <t>0x74cee3640eed67802d8602418d415d7e5f881528425b4aded0a73b883c57f7c2</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4792,7 +4776,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785064974</t>
+          <t>1785068425</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4802,7 +4786,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>3.007519</t>
+          <t>37.356522</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4819,7 +4803,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x7de08a0243073e49c6e479dead7f166232ecd3480830513fb8953abf4d30f575</t>
+          <t>0x8004902c8df50fb0691955c2dde204aa37aea6ffc9f11cb60795a2b8862e7e34</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4834,22 +4818,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.3188</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>KF Drita -1.5</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4859,27 +4843,27 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Riga FC vs Vardar</t>
+          <t>KF Drita vs Floriana</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Riga FC</t>
+          <t>KF Drita</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Floriana</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x3df545e9e324274c452d3611c5ff53dc80c8487fce47da81056d17c1b4257d63</t>
+          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>L19548393</t>
+          <t>L19556829</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4904,17 +4888,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785064838</t>
+          <t>1785065693</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1785258000</t>
+          <t>1785261600</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>13.333333</t>
+          <t>5.301961</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4931,7 +4915,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x98d07c005cea52102549964e374db87ed764bdb1840c7e4d0822a34701829208</t>
+          <t>0x9d52e065d77a1e2ffa07fa7250522f55f6a20661ddb8ab22b3656a5e5f518751</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4939,15 +4923,19 @@
           <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>11.17999</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.3188</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4955,7 +4943,11 @@
           <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>KF Drita -1.5</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -4963,27 +4955,27 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Riga FC vs Vardar</t>
+          <t>KF Drita vs Floriana</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Riga FC</t>
+          <t>KF Drita</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Floriana</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x3ce984b8d5a4fd077770e33c33bd5244077e868cb901d0b9544238e72630158d</t>
+          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>L19548393</t>
+          <t>L19556829</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -5008,17 +5000,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1785064821</t>
+          <t>1785065679</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>1785258000</t>
+          <t>1785261600</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>22.304219</t>
+          <t>9.003922</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -5035,7 +5027,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x90084d34df7f1c1dba6533a65ec3b370264b980f4ee2f405409784667aef3385</t>
+          <t>0xf072d053c048f056d7fa49c75da51e0772df0db003eaf3ddf341cb2fcc16c416</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5050,12 +5042,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.3188</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -5120,7 +5112,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1785064821</t>
+          <t>1785065519</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5130,7 +5122,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>39.205882</t>
+          <t>14.117647</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5147,7 +5139,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0xd382b16331a33a8ef623d9f672b5567e3faaf5a8c56a6b1abbd17c5b3bf2447a</t>
+          <t>0xe1a18ecff833fc919588fdf2e22421fae16e5d31600f43cd14887e49499b233e</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5162,22 +5154,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.3325</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>KF Drita -1.5</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5187,27 +5179,27 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Riga FC vs Vardar</t>
+          <t>KF Drita vs Floriana</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Riga FC</t>
+          <t>KF Drita</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Floriana</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0x3df545e9e324274c452d3611c5ff53dc80c8487fce47da81056d17c1b4257d63</t>
+          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>L19548393</t>
+          <t>L19556829</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5232,17 +5224,17 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1785064819</t>
+          <t>1785065131</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>1785258000</t>
+          <t>1785261600</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>13.888889</t>
+          <t>9.052632</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5259,31 +5251,39 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0xc5ab66578686247686091622e73b8f1713617d5de6c2687bbf706bdd9a1c79eb</t>
+          <t>0x97e956b7b7cfe7d56ae2e8711191f397ae89244a032e763798c4b0021c72d481</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0x594542a29FFceEAeaDD2e67955437c928B51B758</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.2637</t>
+          <t>1.3325</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr"/>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>KF Drita -1.5</t>
+        </is>
+      </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -5291,27 +5291,27 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Riga FC vs Vardar</t>
+          <t>KF Drita vs Floriana</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Riga FC</t>
+          <t>KF Drita</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Floriana</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0x8f444d513fee4c89c59a5fac9732f2bdbc34c255f1e145e912b5e8d3864de79a</t>
+          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>L19548393</t>
+          <t>L19556829</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -5336,17 +5336,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1785064813</t>
+          <t>1785065030</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>1785258000</t>
+          <t>1785261600</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>15.620853</t>
+          <t>11.458647</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5363,7 +5363,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x60648f843dfab3db80e7b11dc76bd422fb1242bf53219948830cbe4d1b29ee2e</t>
+          <t>0x1b6d50b0b2f30b843c8afcdf1bdd77c807787389b518c0d0118f66c5c53154d1</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5378,22 +5378,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.3325</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>KF Drita -1.5</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5403,27 +5403,27 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Riga FC vs Vardar</t>
+          <t>KF Drita vs Floriana</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Riga FC</t>
+          <t>KF Drita</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Floriana</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0x3df545e9e324274c452d3611c5ff53dc80c8487fce47da81056d17c1b4257d63</t>
+          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>L19548393</t>
+          <t>L19556829</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -5448,17 +5448,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1785064792</t>
+          <t>1785064974</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>1785258000</t>
+          <t>1785261600</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>15.444444</t>
+          <t>3.007519</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5475,23 +5475,27 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0xd4092c9aa9c679f18a84f2d088ee1a8595762c53fd62d16b214a853eff1fde81</t>
+          <t>0x7de08a0243073e49c6e479dead7f166232ecd3480830513fb8953abf4d30f575</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0x594542a29FFceEAeaDD2e67955437c928B51B758</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.2637</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5499,7 +5503,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Vardar</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>UEFA Conference League</t>
@@ -5522,7 +5530,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x8f444d513fee4c89c59a5fac9732f2bdbc34c255f1e145e912b5e8d3864de79a</t>
+          <t>0x3df545e9e324274c452d3611c5ff53dc80c8487fce47da81056d17c1b4257d63</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5552,7 +5560,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1785064770</t>
+          <t>1785064838</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5562,7 +5570,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>13.914692</t>
+          <t>13.333333</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5579,28 +5587,28 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x3a9ab01f5b98d3619f0b7d9da475c1eabc0e13099a65941bdca6bd024e7991b6</t>
+          <t>0x98d07c005cea52102549964e374db87ed764bdb1840c7e4d0822a34701829208</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>11.17999</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.2637</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -5626,55 +5634,703 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
+          <t>0x3ce984b8d5a4fd077770e33c33bd5244077e868cb901d0b9544238e72630158d</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>L19548393</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>1785064821</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>1785258000</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>22.304219</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>0x90084d34df7f1c1dba6533a65ec3b370264b980f4ee2f405409784667aef3385</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>13.33</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>KF Drita -1.5</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>KF Drita vs Floriana</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>KF Drita</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Floriana</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0x9a6a1619c23e931d4f7a0e722354bdd7a98d7591c8e2ec98666a74ed9b164c2d</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>L19556829</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>1785064821</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>1785261600</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>39.205882</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>0xd382b16331a33a8ef623d9f672b5567e3faaf5a8c56a6b1abbd17c5b3bf2447a</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Vardar</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Riga FC vs Vardar</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Riga FC</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Vardar</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0x3df545e9e324274c452d3611c5ff53dc80c8487fce47da81056d17c1b4257d63</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>L19548393</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>1785064819</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>1785258000</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>13.888889</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>0xc5ab66578686247686091622e73b8f1713617d5de6c2687bbf706bdd9a1c79eb</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>0x594542a29FFceEAeaDD2e67955437c928B51B758</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>4.12</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>1.2637</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Riga FC vs Vardar</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Riga FC</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Vardar</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
           <t>0x8f444d513fee4c89c59a5fac9732f2bdbc34c255f1e145e912b5e8d3864de79a</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>L19548393</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr">
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>1785064813</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>1785258000</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>15.620853</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>0x60648f843dfab3db80e7b11dc76bd422fb1242bf53219948830cbe4d1b29ee2e</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Vardar</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Riga FC vs Vardar</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Riga FC</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Vardar</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0x3df545e9e324274c452d3611c5ff53dc80c8487fce47da81056d17c1b4257d63</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>L19548393</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>1785064792</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>1785258000</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>15.444444</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>0xd4092c9aa9c679f18a84f2d088ee1a8595762c53fd62d16b214a853eff1fde81</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>0x594542a29FFceEAeaDD2e67955437c928B51B758</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>3.67</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1.2637</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Riga FC vs Vardar</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Riga FC</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Vardar</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>0x8f444d513fee4c89c59a5fac9732f2bdbc34c255f1e145e912b5e8d3864de79a</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>L19548393</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>1785064770</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>1785258000</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>13.914692</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>0x3a9ab01f5b98d3619f0b7d9da475c1eabc0e13099a65941bdca6bd024e7991b6</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1.2637</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Riga FC vs Vardar</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Riga FC</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Vardar</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>0x8f444d513fee4c89c59a5fac9732f2bdbc34c255f1e145e912b5e8d3864de79a</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>L19548393</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
         <is>
           <t>1785064754</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
+      <c r="S54" t="inlineStr">
         <is>
           <t>1785258000</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr">
+      <c r="T54" t="inlineStr">
         <is>
           <t>5.118483</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="U54" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr">
+      <c r="V54" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>
